--- a/gstdatabase/GSTR-1-2024-2025.xlsx
+++ b/gstdatabase/GSTR-1-2024-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6526769B-95AB-4F7C-96A5-AA9AC7224CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92797832-8D43-47B9-B375-619895CFF1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
     <t>FINANCIAL YEAR 2024-2025</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -359,9 +359,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -384,6 +381,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -703,13 +703,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -776,10 +776,10 @@
       <c r="BJ2" s="1"/>
     </row>
     <row r="3" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -906,11 +906,11 @@
       <c r="BJ4" s="1"/>
     </row>
     <row r="5" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -967,100 +967,100 @@
       <c r="BG6" s="1"/>
     </row>
     <row r="8" spans="1:64" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <v>45383</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="14">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="13">
         <v>45413</v>
       </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="14">
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="13">
         <v>45444</v>
       </c>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="14">
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="13">
         <v>45474</v>
       </c>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="14">
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="13">
         <v>45505</v>
       </c>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="15"/>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="14">
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="13">
         <v>45536</v>
       </c>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="15"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="14">
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="15"/>
+      <c r="AG8" s="13">
         <v>45566</v>
       </c>
-      <c r="AH8" s="15"/>
-      <c r="AI8" s="15"/>
-      <c r="AJ8" s="15"/>
-      <c r="AK8" s="16"/>
-      <c r="AL8" s="14">
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
+      <c r="AJ8" s="14"/>
+      <c r="AK8" s="15"/>
+      <c r="AL8" s="13">
         <v>45597</v>
       </c>
-      <c r="AM8" s="15"/>
-      <c r="AN8" s="15"/>
-      <c r="AO8" s="15"/>
-      <c r="AP8" s="16"/>
-      <c r="AQ8" s="14">
+      <c r="AM8" s="14"/>
+      <c r="AN8" s="14"/>
+      <c r="AO8" s="14"/>
+      <c r="AP8" s="15"/>
+      <c r="AQ8" s="13">
         <v>45627</v>
       </c>
-      <c r="AR8" s="15"/>
-      <c r="AS8" s="15"/>
-      <c r="AT8" s="15"/>
-      <c r="AU8" s="16"/>
-      <c r="AV8" s="14">
+      <c r="AR8" s="14"/>
+      <c r="AS8" s="14"/>
+      <c r="AT8" s="14"/>
+      <c r="AU8" s="15"/>
+      <c r="AV8" s="13">
         <v>45658</v>
       </c>
-      <c r="AW8" s="15"/>
-      <c r="AX8" s="15"/>
-      <c r="AY8" s="15"/>
-      <c r="AZ8" s="16"/>
-      <c r="BA8" s="14">
+      <c r="AW8" s="14"/>
+      <c r="AX8" s="14"/>
+      <c r="AY8" s="14"/>
+      <c r="AZ8" s="15"/>
+      <c r="BA8" s="13">
         <v>45689</v>
       </c>
-      <c r="BB8" s="15"/>
-      <c r="BC8" s="15"/>
-      <c r="BD8" s="15"/>
-      <c r="BE8" s="16"/>
-      <c r="BF8" s="14">
+      <c r="BB8" s="14"/>
+      <c r="BC8" s="14"/>
+      <c r="BD8" s="14"/>
+      <c r="BE8" s="15"/>
+      <c r="BF8" s="13">
         <v>45717</v>
       </c>
-      <c r="BG8" s="15"/>
-      <c r="BH8" s="15"/>
-      <c r="BI8" s="15"/>
-      <c r="BJ8" s="16"/>
+      <c r="BG8" s="14"/>
+      <c r="BH8" s="14"/>
+      <c r="BI8" s="14"/>
+      <c r="BJ8" s="15"/>
     </row>
     <row r="9" spans="1:64" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
@@ -1257,14 +1257,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>43283</v>
+        <v>43290</v>
       </c>
       <c r="F10" s="5">
-        <v>72952</v>
+        <v>72959</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>1.0005760526676726</v>
+        <v>1.0006720614456179</v>
       </c>
       <c r="H10" s="5">
         <v>74548</v>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>41344</v>
+        <v>41348</v>
       </c>
       <c r="K10" s="5">
-        <v>74015</v>
+        <v>74019</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.99285024413800504</v>
+        <v>0.99290390084241031</v>
       </c>
       <c r="M10" s="5">
         <v>129395</v>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>81227</v>
+        <v>81233</v>
       </c>
       <c r="P10" s="5">
-        <v>129317</v>
+        <v>129323</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.99939719463657795</v>
+        <v>0.9994435642799181</v>
       </c>
       <c r="R10" s="5">
         <v>72583</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>42538</v>
+        <v>42544</v>
       </c>
       <c r="U10" s="5">
-        <v>72874</v>
+        <v>72880</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>1.004009203256961</v>
+        <v>1.0040918672416406</v>
       </c>
       <c r="W10" s="5">
         <v>74384</v>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>15619</v>
+        <v>15627</v>
       </c>
       <c r="Z10" s="5">
-        <v>73576</v>
+        <v>73584</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.98913744891374489</v>
+        <v>0.98924499892449991</v>
       </c>
       <c r="AB10" s="5">
         <v>130621</v>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>83818</v>
+        <v>83827</v>
       </c>
       <c r="AE10" s="5">
-        <v>130239</v>
+        <v>130248</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.99707550853231874</v>
+        <v>0.99714441016375621</v>
       </c>
       <c r="AG10" s="5">
         <v>72721</v>
@@ -1359,14 +1359,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41924</v>
+        <v>41934</v>
       </c>
       <c r="AJ10" s="5">
-        <v>72604</v>
+        <v>72614</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.9983911112333439</v>
+        <v>0.9985286230937418</v>
       </c>
       <c r="AL10" s="5">
         <v>74187</v>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>41518</v>
+        <v>41530</v>
       </c>
       <c r="AO10" s="5">
-        <v>73707</v>
+        <v>73719</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99352986372275465</v>
+        <v>0.99369161712968579</v>
       </c>
       <c r="AQ10" s="5">
         <v>132270</v>
@@ -1393,14 +1393,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>79369</v>
+        <v>79385</v>
       </c>
       <c r="AT10" s="5">
-        <v>132307</v>
+        <v>132323</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>1.0002797308535571</v>
+        <v>1.0004006955469873</v>
       </c>
       <c r="AV10" s="5">
         <v>73561</v>
@@ -1410,14 +1410,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>41210</v>
+        <v>41226</v>
       </c>
       <c r="AY10" s="5">
-        <v>73457</v>
+        <v>73473</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.99858620736531589</v>
+        <v>0.99880371392449807</v>
       </c>
       <c r="BA10" s="5">
         <v>75582</v>
@@ -1427,14 +1427,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>41446</v>
+        <v>41458</v>
       </c>
       <c r="BD10" s="5">
-        <v>74418</v>
+        <v>74430</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.98459950781932204</v>
+        <v>0.98475827577994757</v>
       </c>
       <c r="BF10" s="5">
         <v>134150</v>
@@ -1444,14 +1444,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>88279</v>
+        <v>88301</v>
       </c>
       <c r="BI10" s="5">
-        <v>133843</v>
+        <v>133865</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>0.99771151695862836</v>
+        <v>0.99787551248602313</v>
       </c>
       <c r="BL10" s="9"/>
     </row>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>14896</v>
+        <v>14899</v>
       </c>
       <c r="F11" s="5">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99198556111815384</v>
+        <v>0.99205002041210977</v>
       </c>
       <c r="H11" s="5">
         <v>47616</v>
@@ -1487,14 +1487,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>15044</v>
+        <v>15047</v>
       </c>
       <c r="K11" s="5">
-        <v>46978</v>
+        <v>46981</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98660114247311825</v>
+        <v>0.98666414650537637</v>
       </c>
       <c r="M11" s="5">
         <v>108402</v>
@@ -1504,14 +1504,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>45264</v>
+        <v>45274</v>
       </c>
       <c r="P11" s="5">
-        <v>108099</v>
+        <v>108109</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99720484861902914</v>
+        <v>0.99729709783952325</v>
       </c>
       <c r="R11" s="5">
         <v>46539</v>
@@ -1521,14 +1521,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>15187</v>
+        <v>15192</v>
       </c>
       <c r="U11" s="5">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99361825565654616</v>
+        <v>0.99372569243000497</v>
       </c>
       <c r="W11" s="5">
         <v>48300</v>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8226</v>
+        <v>8231</v>
       </c>
       <c r="Z11" s="5">
-        <v>46931</v>
+        <v>46936</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97165631469979297</v>
+        <v>0.97175983436852997</v>
       </c>
       <c r="AB11" s="5">
         <v>109219</v>
@@ -1555,14 +1555,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>47723</v>
+        <v>47732</v>
       </c>
       <c r="AE11" s="5">
-        <v>108651</v>
+        <v>108660</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99479943965793494</v>
+        <v>0.99488184290279169</v>
       </c>
       <c r="AG11" s="5">
         <v>46763</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15569</v>
+        <v>15573</v>
       </c>
       <c r="AJ11" s="5">
-        <v>46431</v>
+        <v>46435</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99290036995060194</v>
+        <v>0.99298590766204053</v>
       </c>
       <c r="AL11" s="5">
         <v>48206</v>
@@ -1589,14 +1589,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>14815</v>
+        <v>14819</v>
       </c>
       <c r="AO11" s="5">
-        <v>47159</v>
+        <v>47163</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.97828071194457122</v>
+        <v>0.97836368916732352</v>
       </c>
       <c r="AQ11" s="5">
         <v>110196</v>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>40421</v>
+        <v>40435</v>
       </c>
       <c r="AT11" s="5">
-        <v>109957</v>
+        <v>109971</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99783113724636108</v>
+        <v>0.99795818360013067</v>
       </c>
       <c r="AV11" s="5">
         <v>47206</v>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>14206</v>
+        <v>14209</v>
       </c>
       <c r="AY11" s="5">
-        <v>46818</v>
+        <v>46821</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99178070584247768</v>
+        <v>0.99184425708596369</v>
       </c>
       <c r="BA11" s="5">
         <v>48813</v>
@@ -1640,14 +1640,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>13927</v>
+        <v>13933</v>
       </c>
       <c r="BD11" s="5">
-        <v>47491</v>
+        <v>47497</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97291705078565138</v>
+        <v>0.97303996886075428</v>
       </c>
       <c r="BF11" s="5">
         <v>111276</v>
@@ -1657,14 +1657,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>48227</v>
+        <v>48249</v>
       </c>
       <c r="BI11" s="5">
-        <v>110915</v>
+        <v>110937</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99675581437147276</v>
+        <v>0.99695352097487333</v>
       </c>
       <c r="BL11" s="9"/>
     </row>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>38042</v>
+        <v>38047</v>
       </c>
       <c r="F12" s="5">
-        <v>175286</v>
+        <v>175291</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.98980750009881924</v>
+        <v>0.98983573417056769</v>
       </c>
       <c r="H12" s="5">
         <v>181172</v>
@@ -1700,14 +1700,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>37817</v>
+        <v>37823</v>
       </c>
       <c r="K12" s="5">
-        <v>177959</v>
+        <v>177965</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98226547148566001</v>
+        <v>0.98229858918596691</v>
       </c>
       <c r="M12" s="5">
         <v>363483</v>
@@ -1717,14 +1717,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>99746</v>
+        <v>99755</v>
       </c>
       <c r="P12" s="5">
-        <v>361068</v>
+        <v>361077</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99335594787101456</v>
+        <v>0.99338070831373126</v>
       </c>
       <c r="R12" s="5">
         <v>177513</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>40023</v>
+        <v>40031</v>
       </c>
       <c r="U12" s="5">
-        <v>176833</v>
+        <v>176841</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99616929464320925</v>
+        <v>0.99621436176505385</v>
       </c>
       <c r="W12" s="5">
         <v>182324</v>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>28606</v>
+        <v>28614</v>
       </c>
       <c r="Z12" s="5">
-        <v>178678</v>
+        <v>178686</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.98000263267589571</v>
+        <v>0.98004651060748993</v>
       </c>
       <c r="AB12" s="5">
         <v>365690</v>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>109286</v>
+        <v>109298</v>
       </c>
       <c r="AE12" s="5">
-        <v>363218</v>
+        <v>363230</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99324017610544446</v>
+        <v>0.99327299078454434</v>
       </c>
       <c r="AG12" s="5">
         <v>180670</v>
@@ -1785,14 +1785,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>39881</v>
+        <v>39891</v>
       </c>
       <c r="AJ12" s="5">
-        <v>177042</v>
+        <v>177052</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.97991918968284719</v>
+        <v>0.97997453921514366</v>
       </c>
       <c r="AL12" s="5">
         <v>181581</v>
@@ -1802,14 +1802,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>37308</v>
+        <v>37317</v>
       </c>
       <c r="AO12" s="5">
-        <v>178324</v>
+        <v>178333</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98206310131566632</v>
+        <v>0.98211266597276148</v>
       </c>
       <c r="AQ12" s="5">
         <v>363376</v>
@@ -1819,14 +1819,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>94870</v>
+        <v>94887</v>
       </c>
       <c r="AT12" s="5">
-        <v>362843</v>
+        <v>362860</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99853319977103605</v>
+        <v>0.99857998326801989</v>
       </c>
       <c r="AV12" s="5">
         <v>179534</v>
@@ -1836,14 +1836,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>36455</v>
+        <v>36472</v>
       </c>
       <c r="AY12" s="5">
-        <v>178193</v>
+        <v>178210</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99253066271569734</v>
+        <v>0.99262535230095694</v>
       </c>
       <c r="BA12" s="5">
         <v>184469</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>37198</v>
+        <v>37214</v>
       </c>
       <c r="BD12" s="5">
-        <v>181631</v>
+        <v>181647</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98461530121592244</v>
+        <v>0.98470203665656564</v>
       </c>
       <c r="BF12" s="5">
         <v>368393</v>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>111048</v>
+        <v>111077</v>
       </c>
       <c r="BI12" s="5">
-        <v>367882</v>
+        <v>367911</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.99861289438181511</v>
+        <v>0.99869161466151635</v>
       </c>
       <c r="BL12" s="9"/>
     </row>
@@ -1896,14 +1896,14 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="F13" s="5">
-        <v>17542</v>
+        <v>17543</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="1"/>
-        <v>0.99982901111427758</v>
+        <v>0.99988600740951838</v>
       </c>
       <c r="H13" s="5">
         <v>17787</v>
@@ -1913,14 +1913,14 @@
       </c>
       <c r="J13" s="3">
         <f t="shared" si="2"/>
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="K13" s="5">
-        <v>17660</v>
+        <v>17661</v>
       </c>
       <c r="L13" s="4">
         <f t="shared" si="3"/>
-        <v>0.9928599538989149</v>
+        <v>0.99291617473435656</v>
       </c>
       <c r="M13" s="5">
         <v>28677</v>
@@ -1930,14 +1930,14 @@
       </c>
       <c r="O13" s="3">
         <f t="shared" si="4"/>
-        <v>6816</v>
+        <v>6817</v>
       </c>
       <c r="P13" s="5">
-        <v>28680</v>
+        <v>28681</v>
       </c>
       <c r="Q13" s="4">
         <f t="shared" si="5"/>
-        <v>1.00010461345329</v>
+        <v>1.0001394846043867</v>
       </c>
       <c r="R13" s="5">
         <v>17606</v>
@@ -1947,14 +1947,14 @@
       </c>
       <c r="T13" s="3">
         <f t="shared" si="6"/>
-        <v>3643</v>
+        <v>3644</v>
       </c>
       <c r="U13" s="5">
-        <v>17595</v>
+        <v>17596</v>
       </c>
       <c r="V13" s="4">
         <f t="shared" si="7"/>
-        <v>0.99937521299556964</v>
+        <v>0.99943201181415431</v>
       </c>
       <c r="W13" s="5">
         <v>17849</v>
@@ -1964,14 +1964,14 @@
       </c>
       <c r="Y13" s="3">
         <f t="shared" si="8"/>
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="Z13" s="5">
-        <v>17731</v>
+        <v>17732</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="9"/>
-        <v>0.99338898537733211</v>
+        <v>0.99344501092498183</v>
       </c>
       <c r="AB13" s="5">
         <v>28890</v>
@@ -1981,14 +1981,14 @@
       </c>
       <c r="AD13" s="3">
         <f t="shared" si="10"/>
-        <v>7338</v>
+        <v>7339</v>
       </c>
       <c r="AE13" s="5">
-        <v>28865</v>
+        <v>28866</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="11"/>
-        <v>0.9991346486673589</v>
+        <v>0.99916926272066464</v>
       </c>
       <c r="AG13" s="5">
         <v>17747</v>
@@ -1998,14 +1998,14 @@
       </c>
       <c r="AI13" s="3">
         <f t="shared" si="12"/>
-        <v>3748</v>
+        <v>3749</v>
       </c>
       <c r="AJ13" s="5">
-        <v>17797</v>
+        <v>17798</v>
       </c>
       <c r="AK13" s="4">
         <f t="shared" si="13"/>
-        <v>1.0028173775849438</v>
+        <v>1.0028737251366429</v>
       </c>
       <c r="AL13" s="5">
         <v>17937</v>
@@ -2015,14 +2015,14 @@
       </c>
       <c r="AN13" s="3">
         <f t="shared" si="14"/>
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="AO13" s="5">
-        <v>17839</v>
+        <v>17840</v>
       </c>
       <c r="AP13" s="4">
         <f t="shared" si="15"/>
-        <v>0.99453643307130513</v>
+        <v>0.99459218375425096</v>
       </c>
       <c r="AQ13" s="5">
         <v>28933</v>
@@ -2032,14 +2032,14 @@
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="16"/>
-        <v>6295</v>
+        <v>6297</v>
       </c>
       <c r="AT13" s="5">
-        <v>29020</v>
+        <v>29022</v>
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="17"/>
-        <v>1.0030069470846439</v>
+        <v>1.0030760723049805</v>
       </c>
       <c r="AV13" s="5">
         <v>17858</v>
@@ -2049,14 +2049,14 @@
       </c>
       <c r="AX13" s="3">
         <f t="shared" si="18"/>
-        <v>3284</v>
+        <v>3285</v>
       </c>
       <c r="AY13" s="5">
-        <v>17834</v>
+        <v>17835</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="19"/>
-        <v>0.99865606450890354</v>
+        <v>0.99871206182103256</v>
       </c>
       <c r="BA13" s="5">
         <v>18026</v>
@@ -2066,14 +2066,14 @@
       </c>
       <c r="BC13" s="3">
         <f t="shared" si="20"/>
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="BD13" s="5">
-        <v>17921</v>
+        <v>17922</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="21"/>
-        <v>0.99417508043936531</v>
+        <v>0.99423055586375231</v>
       </c>
       <c r="BF13" s="5">
         <v>29023</v>
@@ -2083,14 +2083,14 @@
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="22"/>
-        <v>7425</v>
+        <v>7428</v>
       </c>
       <c r="BI13" s="5">
-        <v>29136</v>
+        <v>29139</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="23"/>
-        <v>1.0038934638045689</v>
+        <v>1.0039968301002653</v>
       </c>
       <c r="BL13" s="9"/>
     </row>
@@ -2109,14 +2109,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>38213</v>
+        <v>38217</v>
       </c>
       <c r="F14" s="5">
-        <v>89620</v>
+        <v>89624</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.99062651987443073</v>
+        <v>0.99067073440332498</v>
       </c>
       <c r="H14" s="5">
         <v>94129</v>
@@ -2126,14 +2126,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>38651</v>
+        <v>38658</v>
       </c>
       <c r="K14" s="5">
-        <v>91161</v>
+        <v>91168</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.96846880345058373</v>
+        <v>0.96854316948018149</v>
       </c>
       <c r="M14" s="5">
         <v>164995</v>
@@ -2143,14 +2143,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>80951</v>
+        <v>80965</v>
       </c>
       <c r="P14" s="5">
-        <v>164120</v>
+        <v>164134</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99469680899421198</v>
+        <v>0.99478166005030455</v>
       </c>
       <c r="R14" s="5">
         <v>91074</v>
@@ -2160,14 +2160,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>39516</v>
+        <v>39526</v>
       </c>
       <c r="U14" s="5">
-        <v>90538</v>
+        <v>90548</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.99411467597777636</v>
+        <v>0.99422447679908643</v>
       </c>
       <c r="W14" s="5">
         <v>93800</v>
@@ -2177,14 +2177,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>18340</v>
+        <v>18354</v>
       </c>
       <c r="Z14" s="5">
-        <v>91123</v>
+        <v>91137</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.97146055437100209</v>
+        <v>0.97160980810234543</v>
       </c>
       <c r="AB14" s="5">
         <v>166352</v>
@@ -2194,14 +2194,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>85349</v>
+        <v>85370</v>
       </c>
       <c r="AE14" s="5">
-        <v>164832</v>
+        <v>164853</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99086274886986636</v>
+        <v>0.99098898720784845</v>
       </c>
       <c r="AG14" s="5">
         <v>92175</v>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>39775</v>
+        <v>39788</v>
       </c>
       <c r="AJ14" s="5">
-        <v>91281</v>
+        <v>91294</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99030105777054511</v>
+        <v>0.99044209384323301</v>
       </c>
       <c r="AL14" s="5">
         <v>94655</v>
@@ -2228,14 +2228,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>38550</v>
+        <v>38563</v>
       </c>
       <c r="AO14" s="5">
-        <v>92791</v>
+        <v>92804</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.98030743225397499</v>
+        <v>0.98044477312344835</v>
       </c>
       <c r="AQ14" s="5">
         <v>168400</v>
@@ -2245,14 +2245,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>78424</v>
+        <v>78446</v>
       </c>
       <c r="AT14" s="5">
-        <v>167836</v>
+        <v>167858</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>0.99665083135391919</v>
+        <v>0.99678147268408546</v>
       </c>
       <c r="AV14" s="5">
         <v>94024</v>
@@ -2262,14 +2262,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>38194</v>
+        <v>38206</v>
       </c>
       <c r="AY14" s="5">
-        <v>93281</v>
+        <v>93293</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.99209776227346214</v>
+        <v>0.99222538926231596</v>
       </c>
       <c r="BA14" s="5">
         <v>96514</v>
@@ -2279,14 +2279,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>38298</v>
+        <v>38317</v>
       </c>
       <c r="BD14" s="5">
-        <v>94763</v>
+        <v>94782</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.98185755434444744</v>
+        <v>0.98205441697577556</v>
       </c>
       <c r="BF14" s="5">
         <v>171502</v>
@@ -2296,14 +2296,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>86405</v>
+        <v>86438</v>
       </c>
       <c r="BI14" s="5">
-        <v>171113</v>
+        <v>171146</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.99773180487691104</v>
+        <v>0.99792422245804713</v>
       </c>
       <c r="BL14" s="9"/>
     </row>
@@ -2322,14 +2322,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>75148</v>
+        <v>75150</v>
       </c>
       <c r="F15" s="5">
-        <v>301292</v>
+        <v>301294</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.98929900082416411</v>
+        <v>0.98930556786876422</v>
       </c>
       <c r="H15" s="5">
         <v>309950</v>
@@ -2339,14 +2339,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>73620</v>
+        <v>73624</v>
       </c>
       <c r="K15" s="5">
-        <v>306249</v>
+        <v>306253</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.98805936441361508</v>
+        <v>0.98807226972092277</v>
       </c>
       <c r="M15" s="5">
         <v>517862</v>
@@ -2356,14 +2356,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>147249</v>
+        <v>147254</v>
       </c>
       <c r="P15" s="5">
-        <v>514090</v>
+        <v>514095</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99271620624799661</v>
+        <v>0.9927258613298523</v>
       </c>
       <c r="R15" s="5">
         <v>307768</v>
@@ -2373,14 +2373,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>77319</v>
+        <v>77323</v>
       </c>
       <c r="U15" s="5">
-        <v>305837</v>
+        <v>305841</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.99372579345481016</v>
+        <v>0.99373879025759659</v>
       </c>
       <c r="W15" s="5">
         <v>314114</v>
@@ -2390,14 +2390,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>50835</v>
+        <v>50839</v>
       </c>
       <c r="Z15" s="5">
-        <v>308396</v>
+        <v>308400</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98179641786103133</v>
+        <v>0.98180915209127895</v>
       </c>
       <c r="AB15" s="5">
         <v>523203</v>
@@ -2407,14 +2407,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>165277</v>
+        <v>165286</v>
       </c>
       <c r="AE15" s="5">
-        <v>520367</v>
+        <v>520376</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.9945795417839729</v>
+        <v>0.99459674352020155</v>
       </c>
       <c r="AG15" s="5">
         <v>312916</v>
@@ -2424,14 +2424,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>80004</v>
+        <v>80011</v>
       </c>
       <c r="AJ15" s="5">
-        <v>310197</v>
+        <v>310204</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99131076710682742</v>
+        <v>0.99133313732758954</v>
       </c>
       <c r="AL15" s="5">
         <v>318942</v>
@@ -2441,14 +2441,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>75121</v>
+        <v>75129</v>
       </c>
       <c r="AO15" s="5">
-        <v>313638</v>
+        <v>313646</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.98337001711909999</v>
+        <v>0.98339510004953878</v>
       </c>
       <c r="AQ15" s="5">
         <v>530087</v>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>137459</v>
+        <v>137472</v>
       </c>
       <c r="AT15" s="5">
-        <v>527616</v>
+        <v>527629</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.99533850103850874</v>
+        <v>0.99536302531471244</v>
       </c>
       <c r="AV15" s="5">
         <v>317508</v>
@@ -2475,14 +2475,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>73258</v>
+        <v>73267</v>
       </c>
       <c r="AY15" s="5">
-        <v>315855</v>
+        <v>315864</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.99479383196643867</v>
+        <v>0.99482217770890813</v>
       </c>
       <c r="BA15" s="5">
         <v>324414</v>
@@ -2492,14 +2492,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>73959</v>
+        <v>73970</v>
       </c>
       <c r="BD15" s="5">
-        <v>320479</v>
+        <v>320490</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.98787043715745926</v>
+        <v>0.98790434444875996</v>
       </c>
       <c r="BF15" s="5">
         <v>538701</v>
@@ -2509,14 +2509,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>165668</v>
+        <v>165691</v>
       </c>
       <c r="BI15" s="5">
-        <v>537343</v>
+        <v>537366</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99747912107087233</v>
+        <v>0.99752181636937742</v>
       </c>
       <c r="BL15" s="9"/>
     </row>
@@ -2535,14 +2535,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>111667</v>
+        <v>111682</v>
       </c>
       <c r="F16" s="5">
-        <v>439429</v>
+        <v>439444</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.98597866621192876</v>
+        <v>0.98601232279807394</v>
       </c>
       <c r="H16" s="5">
         <v>453561</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>110157</v>
+        <v>110173</v>
       </c>
       <c r="K16" s="5">
-        <v>444386</v>
+        <v>444402</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.97977118843992317</v>
+        <v>0.97980646484155387</v>
       </c>
       <c r="M16" s="5">
         <v>776551</v>
@@ -2569,14 +2569,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>204027</v>
+        <v>204063</v>
       </c>
       <c r="P16" s="5">
-        <v>770627</v>
+        <v>770663</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.99237139608345104</v>
+        <v>0.99241775491886564</v>
       </c>
       <c r="R16" s="5">
         <v>446959</v>
@@ -2586,14 +2586,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>114197</v>
+        <v>114216</v>
       </c>
       <c r="U16" s="5">
-        <v>442993</v>
+        <v>443012</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.99112670289668625</v>
+        <v>0.99116921238860833</v>
       </c>
       <c r="W16" s="5">
         <v>453618</v>
@@ -2603,14 +2603,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>73669</v>
+        <v>73694</v>
       </c>
       <c r="Z16" s="5">
-        <v>443016</v>
+        <v>443041</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.97662791159080986</v>
+        <v>0.97668302404225582</v>
       </c>
       <c r="AB16" s="5">
         <v>775718</v>
@@ -2620,14 +2620,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>220995</v>
+        <v>221053</v>
       </c>
       <c r="AE16" s="5">
-        <v>769458</v>
+        <v>769516</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99193005705681703</v>
+        <v>0.99200482649622668</v>
       </c>
       <c r="AG16" s="5">
         <v>444751</v>
@@ -2637,14 +2637,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>115435</v>
+        <v>115471</v>
       </c>
       <c r="AJ16" s="5">
-        <v>438812</v>
+        <v>438848</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98664646060379857</v>
+        <v>0.98672740477255816</v>
       </c>
       <c r="AL16" s="5">
         <v>448369</v>
@@ -2654,14 +2654,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>107772</v>
+        <v>107813</v>
       </c>
       <c r="AO16" s="5">
-        <v>440037</v>
+        <v>440078</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.98141709172578839</v>
+        <v>0.98150853426530382</v>
       </c>
       <c r="AQ16" s="5">
         <v>770483</v>
@@ -2671,14 +2671,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>183068</v>
+        <v>183161</v>
       </c>
       <c r="AT16" s="5">
-        <v>768896</v>
+        <v>768989</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.99794025306204026</v>
+        <v>0.99806095656880167</v>
       </c>
       <c r="AV16" s="5">
         <v>444563</v>
@@ -2688,14 +2688,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>108670</v>
+        <v>108718</v>
       </c>
       <c r="AY16" s="5">
-        <v>443367</v>
+        <v>443415</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.99730971763282139</v>
+        <v>0.99741768883150417</v>
       </c>
       <c r="BA16" s="5">
         <v>453397</v>
@@ -2705,14 +2705,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>106108</v>
+        <v>106160</v>
       </c>
       <c r="BD16" s="5">
-        <v>447995</v>
+        <v>448047</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.9880854968162559</v>
+        <v>0.98820018659144193</v>
       </c>
       <c r="BF16" s="5">
         <v>780218</v>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>217258</v>
+        <v>217371</v>
       </c>
       <c r="BI16" s="5">
-        <v>779076</v>
+        <v>779189</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.9985363065194599</v>
+        <v>0.99868113783583567</v>
       </c>
       <c r="BL16" s="9"/>
     </row>
@@ -2748,14 +2748,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>91945</v>
+        <v>91953</v>
       </c>
       <c r="F17" s="5">
-        <v>320891</v>
+        <v>320899</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99051132066735603</v>
+        <v>0.99053601469294528</v>
       </c>
       <c r="H17" s="5">
         <v>333085</v>
@@ -2765,14 +2765,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>90223</v>
+        <v>90232</v>
       </c>
       <c r="K17" s="5">
-        <v>328273</v>
+        <v>328282</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98555323716168541</v>
+        <v>0.9855802572916823</v>
       </c>
       <c r="M17" s="5">
         <v>731481</v>
@@ -2782,14 +2782,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>270457</v>
+        <v>270480</v>
       </c>
       <c r="P17" s="5">
-        <v>728740</v>
+        <v>728763</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99625280766007596</v>
+        <v>0.99628425071874727</v>
       </c>
       <c r="R17" s="5">
         <v>324758</v>
@@ -2799,14 +2799,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>95233</v>
+        <v>95247</v>
       </c>
       <c r="U17" s="5">
-        <v>323179</v>
+        <v>323193</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99513791808053997</v>
+        <v>0.9951810271032584</v>
       </c>
       <c r="W17" s="5">
         <v>336053</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>55997</v>
+        <v>56019</v>
       </c>
       <c r="Z17" s="5">
-        <v>326883</v>
+        <v>326905</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.97271263758990401</v>
+        <v>0.97277810345391946</v>
       </c>
       <c r="AB17" s="5">
         <v>736224</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>294194</v>
+        <v>294230</v>
       </c>
       <c r="AE17" s="5">
-        <v>730640</v>
+        <v>730676</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99241535184943708</v>
+        <v>0.99246425001086624</v>
       </c>
       <c r="AG17" s="5">
         <v>328692</v>
@@ -2850,14 +2850,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>97341</v>
+        <v>97363</v>
       </c>
       <c r="AJ17" s="5">
-        <v>325792</v>
+        <v>325814</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.9911771506455892</v>
+        <v>0.99124408260620889</v>
       </c>
       <c r="AL17" s="5">
         <v>339621</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>93191</v>
+        <v>93217</v>
       </c>
       <c r="AO17" s="5">
-        <v>332324</v>
+        <v>332350</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.97851428504126658</v>
+        <v>0.97859084096684246</v>
       </c>
       <c r="AQ17" s="5">
         <v>745574</v>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>256060</v>
+        <v>256111</v>
       </c>
       <c r="AT17" s="5">
-        <v>741926</v>
+        <v>741977</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99510712551671598</v>
+        <v>0.99517552918959085</v>
       </c>
       <c r="AV17" s="5">
         <v>334329</v>
@@ -2901,14 +2901,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>91244</v>
+        <v>91272</v>
       </c>
       <c r="AY17" s="5">
-        <v>332178</v>
+        <v>332206</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99356621770770703</v>
+        <v>0.99364996754693735</v>
       </c>
       <c r="BA17" s="5">
         <v>348862</v>
@@ -2918,14 +2918,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>92928</v>
+        <v>92961</v>
       </c>
       <c r="BD17" s="5">
-        <v>339589</v>
+        <v>339622</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.97341928900252817</v>
+        <v>0.97351388228009927</v>
       </c>
       <c r="BF17" s="5">
         <v>757181</v>
@@ -2935,14 +2935,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>300233</v>
+        <v>300322</v>
       </c>
       <c r="BI17" s="5">
-        <v>755710</v>
+        <v>755799</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.99805726768104319</v>
+        <v>0.998174808929437</v>
       </c>
       <c r="BL17" s="9"/>
     </row>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>482442</v>
+        <v>482468</v>
       </c>
       <c r="F18" s="5">
-        <v>988456</v>
+        <v>988482</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.98998850220140777</v>
+        <v>0.99001454251180832</v>
       </c>
       <c r="H18" s="5">
         <v>1018686</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>481962</v>
+        <v>481998</v>
       </c>
       <c r="K18" s="5">
-        <v>1002021</v>
+        <v>1002057</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.9836406900654372</v>
+        <v>0.98367602970886026</v>
       </c>
       <c r="M18" s="5">
         <v>1536859</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>796324</v>
+        <v>796381</v>
       </c>
       <c r="P18" s="5">
-        <v>1524919</v>
+        <v>1524976</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99223090732461472</v>
+        <v>0.99226799595798965</v>
       </c>
       <c r="R18" s="5">
         <v>1011292</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>495128</v>
+        <v>495168</v>
       </c>
       <c r="U18" s="5">
-        <v>1002712</v>
+        <v>1002752</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.9915158035463546</v>
+        <v>0.99155535690977481</v>
       </c>
       <c r="W18" s="5">
         <v>1030498</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>182394</v>
+        <v>182437</v>
       </c>
       <c r="Z18" s="5">
-        <v>1008712</v>
+        <v>1008755</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.97885876537363492</v>
+        <v>0.97890049277145608</v>
       </c>
       <c r="AB18" s="5">
         <v>1557879</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>828050</v>
+        <v>828129</v>
       </c>
       <c r="AE18" s="5">
-        <v>1541536</v>
+        <v>1541615</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.98950945484212827</v>
+        <v>0.98956016481382703</v>
       </c>
       <c r="AG18" s="5">
         <v>1025067</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>507343</v>
+        <v>507395</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1017867</v>
+        <v>1017919</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.99297606888135115</v>
+        <v>0.99302679727276366</v>
       </c>
       <c r="AL18" s="5">
         <v>1045736</v>
@@ -3080,14 +3080,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>496147</v>
+        <v>496212</v>
       </c>
       <c r="AO18" s="5">
-        <v>1031936</v>
+        <v>1032001</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98680355271311304</v>
+        <v>0.98686570989236289</v>
       </c>
       <c r="AQ18" s="5">
         <v>1584961</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>771437</v>
+        <v>771551</v>
       </c>
       <c r="AT18" s="5">
-        <v>1574899</v>
+        <v>1575013</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.9936515788085637</v>
+        <v>0.99372350486857408</v>
       </c>
       <c r="AV18" s="5">
         <v>1051416</v>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>501303</v>
+        <v>501375</v>
       </c>
       <c r="AY18" s="5">
-        <v>1044831</v>
+        <v>1044903</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99373701750781807</v>
+        <v>0.9938054965874592</v>
       </c>
       <c r="BA18" s="5">
         <v>1075670</v>
@@ -3131,14 +3131,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>500689</v>
+        <v>500776</v>
       </c>
       <c r="BD18" s="5">
-        <v>1060677</v>
+        <v>1060764</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98606171037585877</v>
+        <v>0.98614259019959649</v>
       </c>
       <c r="BF18" s="5">
         <v>1620029</v>
@@ -3148,14 +3148,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>863757</v>
+        <v>863918</v>
       </c>
       <c r="BI18" s="5">
-        <v>1609539</v>
+        <v>1609700</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.99352480727196857</v>
+        <v>0.99362418820897647</v>
       </c>
       <c r="BL18" s="9"/>
     </row>
@@ -3174,14 +3174,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>172043</v>
+        <v>172066</v>
       </c>
       <c r="F19" s="5">
-        <v>284821</v>
+        <v>284844</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.97754019871981879</v>
+        <v>0.97761913750793683</v>
       </c>
       <c r="H19" s="5">
         <v>301141</v>
@@ -3191,14 +3191,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>156439</v>
+        <v>156467</v>
       </c>
       <c r="K19" s="5">
-        <v>289028</v>
+        <v>289056</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.95977631740613201</v>
+        <v>0.95986929710667102</v>
       </c>
       <c r="M19" s="5">
         <v>505864</v>
@@ -3208,14 +3208,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>245315</v>
+        <v>245366</v>
       </c>
       <c r="P19" s="5">
-        <v>498026</v>
+        <v>498077</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98450571695159173</v>
+        <v>0.98460653456264924</v>
       </c>
       <c r="R19" s="5">
         <v>293000</v>
@@ -3225,14 +3225,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>124445</v>
+        <v>124475</v>
       </c>
       <c r="U19" s="5">
-        <v>286455</v>
+        <v>286485</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.97766211604095565</v>
+        <v>0.9777645051194539</v>
       </c>
       <c r="W19" s="5">
         <v>302979</v>
@@ -3242,14 +3242,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>59508</v>
+        <v>59541</v>
       </c>
       <c r="Z19" s="5">
-        <v>287568</v>
+        <v>287601</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.949135088570495</v>
+        <v>0.9492440070103868</v>
       </c>
       <c r="AB19" s="5">
         <v>514622</v>
@@ -3259,14 +3259,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>298784</v>
+        <v>298859</v>
       </c>
       <c r="AE19" s="5">
-        <v>498869</v>
+        <v>498944</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.96938918273995278</v>
+        <v>0.96953492077680314</v>
       </c>
       <c r="AG19" s="5">
         <v>295766</v>
@@ -3276,14 +3276,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>161745</v>
+        <v>161788</v>
       </c>
       <c r="AJ19" s="5">
-        <v>287250</v>
+        <v>287293</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97120696767038805</v>
+        <v>0.97135235287355548</v>
       </c>
       <c r="AL19" s="5">
         <v>302797</v>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>149832</v>
+        <v>149878</v>
       </c>
       <c r="AO19" s="5">
-        <v>291301</v>
+        <v>291347</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.96203396995346713</v>
+        <v>0.96218588691433538</v>
       </c>
       <c r="AQ19" s="5">
         <v>519490</v>
@@ -3310,14 +3310,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>279168</v>
+        <v>279259</v>
       </c>
       <c r="AT19" s="5">
-        <v>507958</v>
+        <v>508049</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.97780130512618146</v>
+        <v>0.97797647692929601</v>
       </c>
       <c r="AV19" s="5">
         <v>299668</v>
@@ -3327,14 +3327,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>153306</v>
+        <v>153357</v>
       </c>
       <c r="AY19" s="5">
-        <v>294594</v>
+        <v>294645</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98306792850754832</v>
+        <v>0.98323811684931328</v>
       </c>
       <c r="BA19" s="5">
         <v>313772</v>
@@ -3344,14 +3344,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>155067</v>
+        <v>155121</v>
       </c>
       <c r="BD19" s="5">
-        <v>299640</v>
+        <v>299694</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.95496092704256597</v>
+        <v>0.95513302652881715</v>
       </c>
       <c r="BF19" s="5">
         <v>528004</v>
@@ -3361,14 +3361,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>333665</v>
+        <v>333806</v>
       </c>
       <c r="BI19" s="5">
-        <v>518420</v>
+        <v>518561</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.98184862235892156</v>
+        <v>0.98211566579041065</v>
       </c>
       <c r="BL19" s="9"/>
     </row>
@@ -3387,14 +3387,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3807</v>
+        <v>3810</v>
       </c>
       <c r="F20" s="5">
-        <v>6405</v>
+        <v>6408</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.99117920148560812</v>
+        <v>0.99164345403899723</v>
       </c>
       <c r="H20" s="5">
         <v>6957</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3745</v>
+        <v>3748</v>
       </c>
       <c r="K20" s="5">
-        <v>6441</v>
+        <v>6444</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.92583009918068138</v>
+        <v>0.92626131953428203</v>
       </c>
       <c r="M20" s="5">
         <v>9947</v>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5542</v>
+        <v>5543</v>
       </c>
       <c r="P20" s="5">
-        <v>9850</v>
+        <v>9851</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>0.99024831607519859</v>
+        <v>0.99034884889916552</v>
       </c>
       <c r="R20" s="5">
         <v>6587</v>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3684</v>
+        <v>3685</v>
       </c>
       <c r="U20" s="5">
-        <v>6495</v>
+        <v>6496</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>0.98603309549111884</v>
+        <v>0.98618490967056327</v>
       </c>
       <c r="W20" s="5">
         <v>6643</v>
@@ -3455,14 +3455,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="Z20" s="5">
-        <v>6517</v>
+        <v>6519</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>0.98103266596417282</v>
+        <v>0.98133373475839225</v>
       </c>
       <c r="AB20" s="5">
         <v>9927</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>5995</v>
+        <v>5997</v>
       </c>
       <c r="AE20" s="5">
-        <v>9895</v>
+        <v>9897</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>0.99677646821799137</v>
+        <v>0.99697793895436693</v>
       </c>
       <c r="AG20" s="5">
         <v>6546</v>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6493</v>
+        <v>6494</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>0.99190345249007028</v>
+        <v>0.99205621753742745</v>
       </c>
       <c r="AL20" s="5">
         <v>6627</v>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3759</v>
+        <v>3760</v>
       </c>
       <c r="AO20" s="5">
-        <v>6553</v>
+        <v>6554</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.98883355968009656</v>
+        <v>0.98898445752225739</v>
       </c>
       <c r="AQ20" s="5">
         <v>9949</v>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>5477</v>
+        <v>5479</v>
       </c>
       <c r="AT20" s="5">
-        <v>9988</v>
+        <v>9990</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>1.003919991958991</v>
+        <v>1.0041210171876571</v>
       </c>
       <c r="AV20" s="5">
         <v>6437</v>
@@ -3540,14 +3540,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>3628</v>
+        <v>3629</v>
       </c>
       <c r="AY20" s="5">
-        <v>6429</v>
+        <v>6430</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.99875718502407951</v>
+        <v>0.99891253689606962</v>
       </c>
       <c r="BA20" s="5">
         <v>6564</v>
@@ -3557,14 +3557,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3496</v>
+        <v>3498</v>
       </c>
       <c r="BD20" s="5">
-        <v>6505</v>
+        <v>6507</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.99101157830591102</v>
+        <v>0.99131627056672755</v>
       </c>
       <c r="BF20" s="5">
         <v>10109</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>6033</v>
+        <v>6038</v>
       </c>
       <c r="BI20" s="5">
-        <v>10089</v>
+        <v>10094</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>0.99802156494213079</v>
+        <v>0.99851617370659806</v>
       </c>
       <c r="BL20" s="9"/>
     </row>
@@ -3600,14 +3600,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>8244</v>
+        <v>8250</v>
       </c>
       <c r="F21" s="5">
-        <v>10903</v>
+        <v>10909</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.99235460089196326</v>
+        <v>0.99290070082825155</v>
       </c>
       <c r="H21" s="5">
         <v>10970</v>
@@ -3617,14 +3617,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>7961</v>
+        <v>7968</v>
       </c>
       <c r="K21" s="5">
-        <v>10961</v>
+        <v>10968</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.99917958067456702</v>
+        <v>0.99981768459434828</v>
       </c>
       <c r="M21" s="5">
         <v>14288</v>
@@ -3634,14 +3634,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>10739</v>
+        <v>10746</v>
       </c>
       <c r="P21" s="5">
-        <v>14568</v>
+        <v>14575</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0195968645016797</v>
+        <v>1.0200867861142218</v>
       </c>
       <c r="R21" s="5">
         <v>10910</v>
@@ -3651,14 +3651,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>8291</v>
+        <v>8297</v>
       </c>
       <c r="U21" s="5">
-        <v>11194</v>
+        <v>11200</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0260311640696609</v>
+        <v>1.0265811182401468</v>
       </c>
       <c r="W21" s="5">
         <v>11256</v>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>3692</v>
+        <v>3699</v>
       </c>
       <c r="Z21" s="5">
-        <v>11331</v>
+        <v>11338</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.0066631130063965</v>
+        <v>1.0072850035536602</v>
       </c>
       <c r="AB21" s="5">
         <v>14831</v>
@@ -3685,14 +3685,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>11319</v>
+        <v>11327</v>
       </c>
       <c r="AE21" s="5">
-        <v>15022</v>
+        <v>15030</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.012878430314881</v>
+        <v>1.013417841008698</v>
       </c>
       <c r="AG21" s="5">
         <v>11222</v>
@@ -3702,14 +3702,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>8209</v>
+        <v>8218</v>
       </c>
       <c r="AJ21" s="5">
-        <v>11369</v>
+        <v>11378</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0130992692924612</v>
+        <v>1.0139012653715915</v>
       </c>
       <c r="AL21" s="5">
         <v>11337</v>
@@ -3719,14 +3719,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>8346</v>
+        <v>8355</v>
       </c>
       <c r="AO21" s="5">
-        <v>11548</v>
+        <v>11557</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>1.0186116256505249</v>
+        <v>1.0194054864602629</v>
       </c>
       <c r="AQ21" s="5">
         <v>15149</v>
@@ -3736,14 +3736,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>11009</v>
+        <v>11023</v>
       </c>
       <c r="AT21" s="5">
-        <v>15425</v>
+        <v>15439</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.0182190243580433</v>
+        <v>1.0191431777675095</v>
       </c>
       <c r="AV21" s="5">
         <v>11422</v>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>8434</v>
+        <v>8443</v>
       </c>
       <c r="AY21" s="5">
-        <v>11716</v>
+        <v>11725</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>1.0257398003852216</v>
+        <v>1.0265277534582384</v>
       </c>
       <c r="BA21" s="5">
         <v>11689</v>
@@ -3770,14 +3770,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>8395</v>
+        <v>8403</v>
       </c>
       <c r="BD21" s="5">
-        <v>11872</v>
+        <v>11880</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>1.0156557447172556</v>
+        <v>1.0163401488579007</v>
       </c>
       <c r="BF21" s="5">
         <v>15725</v>
@@ -3787,14 +3787,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>11924</v>
+        <v>11940</v>
       </c>
       <c r="BI21" s="5">
-        <v>15862</v>
+        <v>15878</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>1.0087122416534182</v>
+        <v>1.0097297297297296</v>
       </c>
       <c r="BL21" s="9"/>
     </row>
@@ -3813,14 +3813,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4623</v>
+        <v>4628</v>
       </c>
       <c r="F22" s="5">
-        <v>6695</v>
+        <v>6700</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.99097098875074008</v>
+        <v>0.9917110716400237</v>
       </c>
       <c r="H22" s="5">
         <v>6770</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4639</v>
+        <v>4644</v>
       </c>
       <c r="K22" s="5">
-        <v>6776</v>
+        <v>6781</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>1.0008862629246678</v>
+        <v>1.0016248153618907</v>
       </c>
       <c r="M22" s="5">
         <v>8074</v>
@@ -3847,14 +3847,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5531</v>
+        <v>5536</v>
       </c>
       <c r="P22" s="5">
-        <v>8098</v>
+        <v>8103</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.0029725043349023</v>
+        <v>1.0035917760713402</v>
       </c>
       <c r="R22" s="5">
         <v>6748</v>
@@ -3864,14 +3864,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4630</v>
+        <v>4635</v>
       </c>
       <c r="U22" s="5">
-        <v>6797</v>
+        <v>6802</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>1.0072614107883817</v>
+        <v>1.0080023710729105</v>
       </c>
       <c r="W22" s="5">
         <v>6876</v>
@@ -3881,14 +3881,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="Z22" s="5">
-        <v>6853</v>
+        <v>6858</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.99665503199534611</v>
+        <v>0.99738219895287961</v>
       </c>
       <c r="AB22" s="5">
         <v>8219</v>
@@ -3898,14 +3898,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5748</v>
+        <v>5754</v>
       </c>
       <c r="AE22" s="5">
-        <v>8252</v>
+        <v>8258</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>1.0040150869935516</v>
+        <v>1.004745102810561</v>
       </c>
       <c r="AG22" s="5">
         <v>6901</v>
@@ -3915,14 +3915,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4682</v>
+        <v>4687</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6918</v>
+        <v>6923</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>1.0024634110998405</v>
+        <v>1.0031879437762643</v>
       </c>
       <c r="AL22" s="5">
         <v>6948</v>
@@ -3932,14 +3932,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4654</v>
+        <v>4659</v>
       </c>
       <c r="AO22" s="5">
-        <v>6960</v>
+        <v>6965</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>1.0017271157167531</v>
+        <v>1.0024467472654002</v>
       </c>
       <c r="AQ22" s="5">
         <v>8297</v>
@@ -3949,14 +3949,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5585</v>
+        <v>5591</v>
       </c>
       <c r="AT22" s="5">
-        <v>8323</v>
+        <v>8329</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>1.0031336627696759</v>
+        <v>1.003856815716524</v>
       </c>
       <c r="AV22" s="5">
         <v>6958</v>
@@ -3966,14 +3966,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>4681</v>
+        <v>4687</v>
       </c>
       <c r="AY22" s="5">
-        <v>6999</v>
+        <v>7005</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>1.0058924978442081</v>
+        <v>1.0067548146018972</v>
       </c>
       <c r="BA22" s="5">
         <v>7049</v>
@@ -3983,14 +3983,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4664</v>
+        <v>4670</v>
       </c>
       <c r="BD22" s="5">
-        <v>7059</v>
+        <v>7065</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>1.0014186409419776</v>
+        <v>1.002269825507164</v>
       </c>
       <c r="BF22" s="5">
         <v>8436</v>
@@ -4000,14 +4000,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5782</v>
+        <v>5790</v>
       </c>
       <c r="BI22" s="5">
-        <v>8438</v>
+        <v>8446</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>1.0002370791844477</v>
+        <v>1.0011853959222381</v>
       </c>
       <c r="BL22" s="9"/>
     </row>
@@ -4026,14 +4026,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>6245</v>
+        <v>6247</v>
       </c>
       <c r="F23" s="5">
-        <v>8691</v>
+        <v>8693</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.98671662125340598</v>
+        <v>0.98694368755676654</v>
       </c>
       <c r="H23" s="5">
         <v>8878</v>
@@ -4043,14 +4043,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>6331</v>
+        <v>6334</v>
       </c>
       <c r="K23" s="5">
-        <v>8807</v>
+        <v>8810</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.99200270331155671</v>
+        <v>0.99234061725613876</v>
       </c>
       <c r="M23" s="5">
         <v>11255</v>
@@ -4060,14 +4060,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="P23" s="5">
-        <v>11240</v>
+        <v>11243</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.99866725899600173</v>
+        <v>0.99893380719680147</v>
       </c>
       <c r="R23" s="5">
         <v>8944</v>
@@ -4077,14 +4077,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6241</v>
+        <v>6244</v>
       </c>
       <c r="U23" s="5">
-        <v>8933</v>
+        <v>8936</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.99877012522361364</v>
+        <v>0.99910554561717357</v>
       </c>
       <c r="W23" s="5">
         <v>10422</v>
@@ -4094,14 +4094,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>2967</v>
+        <v>2970</v>
       </c>
       <c r="Z23" s="5">
-        <v>9044</v>
+        <v>9047</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.86777969679524081</v>
+        <v>0.86806754941469966</v>
       </c>
       <c r="AB23" s="5">
         <v>11673</v>
@@ -4111,14 +4111,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>8277</v>
+        <v>8283</v>
       </c>
       <c r="AE23" s="5">
-        <v>11443</v>
+        <v>11449</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.98029641052000338</v>
+        <v>0.98081041720209028</v>
       </c>
       <c r="AG23" s="5">
         <v>9370</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6389</v>
+        <v>6395</v>
       </c>
       <c r="AJ23" s="5">
-        <v>9019</v>
+        <v>9025</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.96254002134471717</v>
+        <v>0.96318036286019215</v>
       </c>
       <c r="AL23" s="5">
         <v>9238</v>
@@ -4145,14 +4145,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>6441</v>
+        <v>6448</v>
       </c>
       <c r="AO23" s="5">
-        <v>9060</v>
+        <v>9067</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.98073176012123842</v>
+        <v>0.98148949989175149</v>
       </c>
       <c r="AQ23" s="5">
         <v>11727</v>
@@ -4162,14 +4162,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>8082</v>
+        <v>8094</v>
       </c>
       <c r="AT23" s="5">
-        <v>11562</v>
+        <v>11574</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>0.98592990534663594</v>
+        <v>0.98695318495778972</v>
       </c>
       <c r="AV23" s="5">
         <v>9359</v>
@@ -4179,14 +4179,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>6496</v>
+        <v>6504</v>
       </c>
       <c r="AY23" s="5">
-        <v>9178</v>
+        <v>9186</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>0.98066032695800831</v>
+        <v>0.9815151191366599</v>
       </c>
       <c r="BA23" s="5">
         <v>9570</v>
@@ -4196,14 +4196,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6435</v>
+        <v>6444</v>
       </c>
       <c r="BD23" s="5">
-        <v>9232</v>
+        <v>9241</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.96468129571577843</v>
+        <v>0.96562173458725187</v>
       </c>
       <c r="BF23" s="5">
         <v>11968</v>
@@ -4213,14 +4213,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>8612</v>
+        <v>8625</v>
       </c>
       <c r="BI23" s="5">
-        <v>11762</v>
+        <v>11775</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.98278743315508021</v>
+        <v>0.98387366310160429</v>
       </c>
       <c r="BL23" s="9"/>
     </row>
@@ -4239,14 +4239,14 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>4838</v>
+        <v>4839</v>
       </c>
       <c r="F24" s="5">
-        <v>6191</v>
+        <v>6192</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>0.99056</v>
+        <v>0.99072000000000005</v>
       </c>
       <c r="H24" s="5">
         <v>6322</v>
@@ -4256,14 +4256,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>4876</v>
+        <v>4877</v>
       </c>
       <c r="K24" s="5">
-        <v>6240</v>
+        <v>6241</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.98702942106928182</v>
+        <v>0.98718759886111995</v>
       </c>
       <c r="M24" s="5">
         <v>7266</v>
@@ -4273,14 +4273,14 @@
       </c>
       <c r="O24" s="3">
         <f t="shared" si="4"/>
-        <v>5675</v>
+        <v>5677</v>
       </c>
       <c r="P24" s="5">
-        <v>7169</v>
+        <v>7171</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="5"/>
-        <v>0.98665015139003576</v>
+        <v>0.98692540600055056</v>
       </c>
       <c r="R24" s="5">
         <v>6403</v>
@@ -4290,14 +4290,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="6"/>
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="U24" s="5">
-        <v>6311</v>
+        <v>6312</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="7"/>
-        <v>0.98563173512416058</v>
+        <v>0.98578791191628923</v>
       </c>
       <c r="W24" s="5">
         <v>6540</v>
@@ -4324,14 +4324,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5854</v>
+        <v>5855</v>
       </c>
       <c r="AE24" s="5">
-        <v>7388</v>
+        <v>7389</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.98862571925598819</v>
+        <v>0.98875953432356478</v>
       </c>
       <c r="AG24" s="5">
         <v>6660</v>
@@ -4426,14 +4426,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="BI24" s="5">
-        <v>7762</v>
+        <v>7763</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.98527545062198529</v>
+        <v>0.98540238639248545</v>
       </c>
       <c r="BL24" s="9"/>
     </row>
@@ -4452,14 +4452,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>11745</v>
+        <v>11748</v>
       </c>
       <c r="F25" s="5">
-        <v>20222</v>
+        <v>20225</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.96626529051987764</v>
+        <v>0.96640863914373087</v>
       </c>
       <c r="H25" s="5">
         <v>20519</v>
@@ -4469,14 +4469,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>11476</v>
+        <v>11480</v>
       </c>
       <c r="K25" s="5">
-        <v>20353</v>
+        <v>20357</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.99190993713143916</v>
+        <v>0.99210487840538042</v>
       </c>
       <c r="M25" s="5">
         <v>27924</v>
@@ -4486,14 +4486,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>16486</v>
+        <v>16490</v>
       </c>
       <c r="P25" s="5">
-        <v>27933</v>
+        <v>27937</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>1.0003223033949291</v>
+        <v>1.0004655493482308</v>
       </c>
       <c r="R25" s="5">
         <v>20481</v>
@@ -4503,14 +4503,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>11666</v>
+        <v>11669</v>
       </c>
       <c r="U25" s="5">
-        <v>20501</v>
+        <v>20504</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>1.0009765148186123</v>
+        <v>1.0011229920414042</v>
       </c>
       <c r="W25" s="5">
         <v>20934</v>
@@ -4520,14 +4520,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>4225</v>
+        <v>4228</v>
       </c>
       <c r="Z25" s="5">
-        <v>20624</v>
+        <v>20627</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.98519155440909523</v>
+        <v>0.98533486194707176</v>
       </c>
       <c r="AB25" s="5">
         <v>28211</v>
@@ -4537,14 +4537,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>18121</v>
+        <v>18130</v>
       </c>
       <c r="AE25" s="5">
-        <v>28252</v>
+        <v>28261</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>1.0014533338059621</v>
+        <v>1.0017723582999538</v>
       </c>
       <c r="AG25" s="5">
         <v>20778</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>11791</v>
+        <v>11799</v>
       </c>
       <c r="AJ25" s="5">
-        <v>20739</v>
+        <v>20747</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>0.99812301472711518</v>
+        <v>0.99850803734719418</v>
       </c>
       <c r="AL25" s="5">
         <v>21081</v>
@@ -4571,14 +4571,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>11861</v>
+        <v>11868</v>
       </c>
       <c r="AO25" s="5">
-        <v>20920</v>
+        <v>20927</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.99236279113894033</v>
+        <v>0.99269484369811678</v>
       </c>
       <c r="AQ25" s="5">
         <v>28478</v>
@@ -4588,14 +4588,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>16501</v>
+        <v>16512</v>
       </c>
       <c r="AT25" s="5">
-        <v>28516</v>
+        <v>28527</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>1.0013343633682141</v>
+        <v>1.0017206264484866</v>
       </c>
       <c r="AV25" s="5">
         <v>21086</v>
@@ -4605,14 +4605,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>12100</v>
+        <v>12108</v>
       </c>
       <c r="AY25" s="5">
-        <v>21066</v>
+        <v>21074</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>0.99905150336716309</v>
+        <v>0.99943090202029783</v>
       </c>
       <c r="BA25" s="5">
         <v>21405</v>
@@ -4622,14 +4622,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>12044</v>
+        <v>12053</v>
       </c>
       <c r="BD25" s="5">
-        <v>21254</v>
+        <v>21263</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>0.99294557346414392</v>
+        <v>0.99336603597290352</v>
       </c>
       <c r="BF25" s="5">
         <v>28924</v>
@@ -4639,14 +4639,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>17910</v>
+        <v>17925</v>
       </c>
       <c r="BI25" s="5">
-        <v>28880</v>
+        <v>28895</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>0.99847877195408652</v>
+        <v>0.99899737242428432</v>
       </c>
       <c r="BL25" s="9"/>
     </row>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>9675</v>
+        <v>9684</v>
       </c>
       <c r="F26" s="5">
-        <v>14046</v>
+        <v>14055</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.99744354495100129</v>
+        <v>0.99808265871325097</v>
       </c>
       <c r="H26" s="5">
         <v>14494</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>9766</v>
+        <v>9773</v>
       </c>
       <c r="K26" s="5">
-        <v>14332</v>
+        <v>14339</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.98882296122533464</v>
+        <v>0.98930591969090653</v>
       </c>
       <c r="M26" s="5">
         <v>27473</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>19047</v>
+        <v>19060</v>
       </c>
       <c r="P26" s="5">
-        <v>27456</v>
+        <v>27469</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>0.99938121064317698</v>
+        <v>0.99985440250427693</v>
       </c>
       <c r="R26" s="5">
         <v>14274</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>10020</v>
+        <v>10029</v>
       </c>
       <c r="U26" s="5">
-        <v>14226</v>
+        <v>14235</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>0.99663724253888186</v>
+        <v>0.99726775956284153</v>
       </c>
       <c r="W26" s="5">
         <v>14651</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>3137</v>
+        <v>3146</v>
       </c>
       <c r="Z26" s="5">
-        <v>14450</v>
+        <v>14459</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.98628079994539619</v>
+        <v>0.98689509248515461</v>
       </c>
       <c r="AB26" s="5">
         <v>28023</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>20320</v>
+        <v>20336</v>
       </c>
       <c r="AE26" s="5">
-        <v>27741</v>
+        <v>27757</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.98993683759768758</v>
+        <v>0.99050779716661319</v>
       </c>
       <c r="AG26" s="5">
         <v>14346</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9777</v>
+        <v>9784</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14259</v>
+        <v>14266</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.99393559180259305</v>
+        <v>0.99442353269203965</v>
       </c>
       <c r="AL26" s="5">
         <v>14687</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="14"/>
-        <v>9462</v>
+        <v>9472</v>
       </c>
       <c r="AO26" s="5">
-        <v>14435</v>
+        <v>14445</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.98284196908830934</v>
+        <v>0.98352284333083684</v>
       </c>
       <c r="AQ26" s="5">
         <v>27948</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="16"/>
-        <v>18823</v>
+        <v>18843</v>
       </c>
       <c r="AT26" s="5">
-        <v>27862</v>
+        <v>27882</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99692285673393444</v>
+        <v>0.99763847144697293</v>
       </c>
       <c r="AV26" s="5">
         <v>14478</v>
@@ -4818,14 +4818,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="18"/>
-        <v>9501</v>
+        <v>9511</v>
       </c>
       <c r="AY26" s="5">
-        <v>14397</v>
+        <v>14407</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.99440530460008292</v>
+        <v>0.99509600773587514</v>
       </c>
       <c r="BA26" s="5">
         <v>14902</v>
@@ -4835,14 +4835,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="20"/>
-        <v>9591</v>
+        <v>9600</v>
       </c>
       <c r="BD26" s="5">
-        <v>14538</v>
+        <v>14547</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.97557374849013556</v>
+        <v>0.97617769426922563</v>
       </c>
       <c r="BF26" s="5">
         <v>28105</v>
@@ -4852,14 +4852,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="22"/>
-        <v>20212</v>
+        <v>20232</v>
       </c>
       <c r="BI26" s="5">
-        <v>27975</v>
+        <v>27995</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.99537448852517341</v>
+        <v>0.99608610567514677</v>
       </c>
       <c r="BL26" s="9"/>
     </row>
@@ -4878,14 +4878,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>76353</v>
+        <v>76376</v>
       </c>
       <c r="F27" s="5">
-        <v>125140</v>
+        <v>125163</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.96904837498160867</v>
+        <v>0.96922648040453163</v>
       </c>
       <c r="H27" s="5">
         <v>129298</v>
@@ -4895,14 +4895,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>74656</v>
+        <v>74681</v>
       </c>
       <c r="K27" s="5">
-        <v>126052</v>
+        <v>126077</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.97489520332874446</v>
+        <v>0.97508855512072889</v>
       </c>
       <c r="M27" s="5">
         <v>186733</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>116767</v>
+        <v>116814</v>
       </c>
       <c r="P27" s="5">
-        <v>185861</v>
+        <v>185908</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.99533023086438921</v>
+        <v>0.99558192713660676</v>
       </c>
       <c r="R27" s="5">
         <v>126872</v>
@@ -4929,14 +4929,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>75196</v>
+        <v>75230</v>
       </c>
       <c r="U27" s="5">
-        <v>125723</v>
+        <v>125757</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99094362822372151</v>
+        <v>0.9912116148559178</v>
       </c>
       <c r="W27" s="5">
         <v>129739</v>
@@ -4946,14 +4946,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>33833</v>
+        <v>33869</v>
       </c>
       <c r="Z27" s="5">
-        <v>126694</v>
+        <v>126730</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.97652980214122198</v>
+        <v>0.97680728231295144</v>
       </c>
       <c r="AB27" s="5">
         <v>188270</v>
@@ -4963,14 +4963,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>125807</v>
+        <v>125868</v>
       </c>
       <c r="AE27" s="5">
-        <v>187295</v>
+        <v>187356</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99482126732883625</v>
+        <v>0.99514527009082698</v>
       </c>
       <c r="AG27" s="5">
         <v>127800</v>
@@ -4980,14 +4980,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>76515</v>
+        <v>76556</v>
       </c>
       <c r="AJ27" s="5">
-        <v>126860</v>
+        <v>126901</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.99264475743348979</v>
+        <v>0.99296557120500784</v>
       </c>
       <c r="AL27" s="5">
         <v>130262</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="14"/>
-        <v>74694</v>
+        <v>74737</v>
       </c>
       <c r="AO27" s="5">
-        <v>127935</v>
+        <v>127978</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="15"/>
-        <v>0.98213600282507563</v>
+        <v>0.98246610676943391</v>
       </c>
       <c r="AQ27" s="5">
         <v>189830</v>
@@ -5014,14 +5014,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="16"/>
-        <v>116125</v>
+        <v>116200</v>
       </c>
       <c r="AT27" s="5">
-        <v>189378</v>
+        <v>189453</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="17"/>
-        <v>0.99761892219354154</v>
+        <v>0.99801401253753363</v>
       </c>
       <c r="AV27" s="5">
         <v>128733</v>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="18"/>
-        <v>73943</v>
+        <v>73987</v>
       </c>
       <c r="AY27" s="5">
-        <v>128604</v>
+        <v>128648</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="19"/>
-        <v>0.99899792593973569</v>
+        <v>0.99933971864246152</v>
       </c>
       <c r="BA27" s="5">
         <v>132099</v>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="20"/>
-        <v>74554</v>
+        <v>74600</v>
       </c>
       <c r="BD27" s="5">
-        <v>130122</v>
+        <v>130168</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="21"/>
-        <v>0.98503395180887066</v>
+        <v>0.98538217548959495</v>
       </c>
       <c r="BF27" s="5">
         <v>192460</v>
@@ -5065,14 +5065,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>123650</v>
+        <v>123749</v>
       </c>
       <c r="BI27" s="5">
-        <v>192028</v>
+        <v>192127</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="23"/>
-        <v>0.99775537774082923</v>
+        <v>0.99826977034188924</v>
       </c>
       <c r="BL27" s="9"/>
     </row>
@@ -5091,14 +5091,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>175706</v>
+        <v>175727</v>
       </c>
       <c r="F28" s="5">
-        <v>409431</v>
+        <v>409452</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99053810162044986</v>
+        <v>0.99058890700678859</v>
       </c>
       <c r="H28" s="5">
         <v>423216</v>
@@ -5108,14 +5108,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>174289</v>
+        <v>174309</v>
       </c>
       <c r="K28" s="5">
-        <v>413858</v>
+        <v>413878</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.97788835960833242</v>
+        <v>0.97793561680087704</v>
       </c>
       <c r="M28" s="5">
         <v>688530</v>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>299396</v>
+        <v>299430</v>
       </c>
       <c r="P28" s="5">
-        <v>682080</v>
+        <v>682114</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.9906322164611564</v>
+        <v>0.99068159702554714</v>
       </c>
       <c r="R28" s="5">
         <v>417505</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>173339</v>
+        <v>173358</v>
       </c>
       <c r="U28" s="5">
-        <v>414140</v>
+        <v>414159</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99194021628483486</v>
+        <v>0.99198572472185964</v>
       </c>
       <c r="W28" s="5">
         <v>426115</v>
@@ -5159,14 +5159,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>67633</v>
+        <v>67654</v>
       </c>
       <c r="Z28" s="5">
-        <v>416298</v>
+        <v>416319</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.9769616183424662</v>
+        <v>0.97701090081316078</v>
       </c>
       <c r="AB28" s="5">
         <v>693825</v>
@@ -5176,14 +5176,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>332173</v>
+        <v>332219</v>
       </c>
       <c r="AE28" s="5">
-        <v>687347</v>
+        <v>687393</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99066335170972508</v>
+        <v>0.99072965084855691</v>
       </c>
       <c r="AG28" s="5">
         <v>421441</v>
@@ -5193,14 +5193,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>172978</v>
+        <v>173001</v>
       </c>
       <c r="AJ28" s="5">
-        <v>416856</v>
+        <v>416879</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.98912065983138797</v>
+        <v>0.98917523449308442</v>
       </c>
       <c r="AL28" s="5">
         <v>428935</v>
@@ -5210,14 +5210,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="14"/>
-        <v>166900</v>
+        <v>166930</v>
       </c>
       <c r="AO28" s="5">
-        <v>421401</v>
+        <v>421431</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="15"/>
-        <v>0.98243556716052549</v>
+        <v>0.98250550782752633</v>
       </c>
       <c r="AQ28" s="5">
         <v>700018</v>
@@ -5227,14 +5227,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="16"/>
-        <v>292451</v>
+        <v>292533</v>
       </c>
       <c r="AT28" s="5">
-        <v>696437</v>
+        <v>696519</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="17"/>
-        <v>0.99488441725784194</v>
+        <v>0.99500155710281735</v>
       </c>
       <c r="AV28" s="5">
         <v>428584</v>
@@ -5244,14 +5244,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="18"/>
-        <v>169679</v>
+        <v>169721</v>
       </c>
       <c r="AY28" s="5">
-        <v>426403</v>
+        <v>426445</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="19"/>
-        <v>0.99491114927295465</v>
+        <v>0.99500914639837235</v>
       </c>
       <c r="BA28" s="5">
         <v>438333</v>
@@ -5261,14 +5261,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="20"/>
-        <v>170347</v>
+        <v>170396</v>
       </c>
       <c r="BD28" s="5">
-        <v>431687</v>
+        <v>431736</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="21"/>
-        <v>0.98483801128365878</v>
+        <v>0.98494979844091135</v>
       </c>
       <c r="BF28" s="5">
         <v>711748</v>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>332176</v>
+        <v>332303</v>
       </c>
       <c r="BI28" s="5">
-        <v>707494</v>
+        <v>707621</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.99402316550239689</v>
+        <v>0.99420159944249931</v>
       </c>
       <c r="BL28" s="9"/>
     </row>
@@ -5304,14 +5304,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>70920</v>
+        <v>70923</v>
       </c>
       <c r="F29" s="5">
-        <v>135496</v>
+        <v>135499</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99051127973449127</v>
+        <v>0.99053321052092924</v>
       </c>
       <c r="H29" s="5">
         <v>138439</v>
@@ -5321,14 +5321,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>70917</v>
+        <v>70921</v>
       </c>
       <c r="K29" s="5">
-        <v>136701</v>
+        <v>136705</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98744573422229287</v>
+        <v>0.98747462781441642</v>
       </c>
       <c r="M29" s="5">
         <v>184711</v>
@@ -5338,14 +5338,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>99005</v>
+        <v>99020</v>
       </c>
       <c r="P29" s="5">
-        <v>183140</v>
+        <v>183155</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.99149482164029212</v>
+        <v>0.99157602958134594</v>
       </c>
       <c r="R29" s="5">
         <v>138323</v>
@@ -5355,14 +5355,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>72707</v>
+        <v>72714</v>
       </c>
       <c r="U29" s="5">
-        <v>136862</v>
+        <v>136869</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.98943776523065574</v>
+        <v>0.98948837142051571</v>
       </c>
       <c r="W29" s="5">
         <v>139858</v>
@@ -5372,14 +5372,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>25792</v>
+        <v>25801</v>
       </c>
       <c r="Z29" s="5">
-        <v>137344</v>
+        <v>137353</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.98202462497676213</v>
+        <v>0.98208897596133216</v>
       </c>
       <c r="AB29" s="5">
         <v>187429</v>
@@ -5389,14 +5389,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>107184</v>
+        <v>107202</v>
       </c>
       <c r="AE29" s="5">
-        <v>184524</v>
+        <v>184542</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.98450079763537124</v>
+        <v>0.98459683400114173</v>
       </c>
       <c r="AG29" s="5">
         <v>139419</v>
@@ -5406,14 +5406,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>74796</v>
+        <v>74807</v>
       </c>
       <c r="AJ29" s="5">
-        <v>138041</v>
+        <v>138052</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.99011612477495892</v>
+        <v>0.99019502363379452</v>
       </c>
       <c r="AL29" s="5">
         <v>141276</v>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="14"/>
-        <v>71136</v>
+        <v>71149</v>
       </c>
       <c r="AO29" s="5">
-        <v>139250</v>
+        <v>139263</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="15"/>
-        <v>0.9856592768764687</v>
+        <v>0.98575129533678751</v>
       </c>
       <c r="AQ29" s="5">
         <v>188424</v>
@@ -5440,14 +5440,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="16"/>
-        <v>97121</v>
+        <v>97149</v>
       </c>
       <c r="AT29" s="5">
-        <v>187228</v>
+        <v>187256</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="17"/>
-        <v>0.9936526132552117</v>
+        <v>0.99380121428268164</v>
       </c>
       <c r="AV29" s="5">
         <v>141887</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="18"/>
-        <v>71706</v>
+        <v>71720</v>
       </c>
       <c r="AY29" s="5">
-        <v>140497</v>
+        <v>140511</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="19"/>
-        <v>0.99020347177683654</v>
+        <v>0.99030214184527121</v>
       </c>
       <c r="BA29" s="5">
         <v>143795</v>
@@ -5474,14 +5474,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="20"/>
-        <v>71482</v>
+        <v>71497</v>
       </c>
       <c r="BD29" s="5">
-        <v>141719</v>
+        <v>141734</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="21"/>
-        <v>0.98556278034702183</v>
+        <v>0.98566709551792486</v>
       </c>
       <c r="BF29" s="5">
         <v>191754</v>
@@ -5491,14 +5491,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>105432</v>
+        <v>105469</v>
       </c>
       <c r="BI29" s="5">
-        <v>189638</v>
+        <v>189675</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.98896502810893128</v>
+        <v>0.98915798366657282</v>
       </c>
       <c r="BL29" s="9"/>
     </row>
@@ -5517,14 +5517,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>100989</v>
+        <v>100999</v>
       </c>
       <c r="F30" s="5">
-        <v>176025</v>
+        <v>176035</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.98753969233531191</v>
+        <v>0.98759579457603541</v>
       </c>
       <c r="H30" s="5">
         <v>181910</v>
@@ -5534,14 +5534,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>100090</v>
+        <v>100101</v>
       </c>
       <c r="K30" s="5">
-        <v>178273</v>
+        <v>178284</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.98000659666868228</v>
+        <v>0.98006706613160355</v>
       </c>
       <c r="M30" s="5">
         <v>304709</v>
@@ -5551,14 +5551,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>185092</v>
+        <v>185110</v>
       </c>
       <c r="P30" s="5">
-        <v>301559</v>
+        <v>301577</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.98966226793432421</v>
+        <v>0.98972134068898521</v>
       </c>
       <c r="R30" s="5">
         <v>179361</v>
@@ -5568,14 +5568,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>100528</v>
+        <v>100537</v>
       </c>
       <c r="U30" s="5">
-        <v>177834</v>
+        <v>177843</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99148644354123805</v>
+        <v>0.99153662167360801</v>
       </c>
       <c r="W30" s="5">
         <v>184404</v>
@@ -5585,14 +5585,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>38549</v>
+        <v>38562</v>
       </c>
       <c r="Z30" s="5">
-        <v>179082</v>
+        <v>179095</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.97113945467560359</v>
+        <v>0.9712099520617774</v>
       </c>
       <c r="AB30" s="5">
         <v>307610</v>
@@ -5602,14 +5602,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>193463</v>
+        <v>193494</v>
       </c>
       <c r="AE30" s="5">
-        <v>304588</v>
+        <v>304619</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.99017587204577229</v>
+        <v>0.99027664900360846</v>
       </c>
       <c r="AG30" s="5">
         <v>180656</v>
@@ -5619,14 +5619,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>99599</v>
+        <v>99615</v>
       </c>
       <c r="AJ30" s="5">
-        <v>178810</v>
+        <v>178826</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.98978168452749982</v>
+        <v>0.98987025064210432</v>
       </c>
       <c r="AL30" s="5">
         <v>185185</v>
@@ -5636,14 +5636,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="14"/>
-        <v>98861</v>
+        <v>98879</v>
       </c>
       <c r="AO30" s="5">
-        <v>181705</v>
+        <v>181723</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="15"/>
-        <v>0.98120798120798125</v>
+        <v>0.9813051813051813</v>
       </c>
       <c r="AQ30" s="5">
         <v>311830</v>
@@ -5653,14 +5653,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>178344</v>
+        <v>178381</v>
       </c>
       <c r="AT30" s="5">
-        <v>309582</v>
+        <v>309619</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="17"/>
-        <v>0.99279094378347177</v>
+        <v>0.99290959817849467</v>
       </c>
       <c r="AV30" s="5">
         <v>184055</v>
@@ -5670,14 +5670,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="18"/>
-        <v>100196</v>
+        <v>100220</v>
       </c>
       <c r="AY30" s="5">
-        <v>182540</v>
+        <v>182564</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="19"/>
-        <v>0.99176876477139986</v>
+        <v>0.99189916057700145</v>
       </c>
       <c r="BA30" s="5">
         <v>188792</v>
@@ -5687,14 +5687,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="20"/>
-        <v>100375</v>
+        <v>100399</v>
       </c>
       <c r="BD30" s="5">
-        <v>184922</v>
+        <v>184946</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="21"/>
-        <v>0.9795012500529684</v>
+        <v>0.97962837408364756</v>
       </c>
       <c r="BF30" s="5">
         <v>315967</v>
@@ -5704,14 +5704,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>193644</v>
+        <v>193691</v>
       </c>
       <c r="BI30" s="5">
-        <v>314045</v>
+        <v>314092</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.99391708627799735</v>
+        <v>0.9940658359892014</v>
       </c>
       <c r="BL30" s="9"/>
     </row>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>35400</v>
+        <v>35403</v>
       </c>
       <c r="F31" s="5">
-        <v>78742</v>
+        <v>78745</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>1.0009788342973369</v>
+        <v>1.0010169706985317</v>
       </c>
       <c r="H31" s="5">
         <v>80911</v>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>33730</v>
+        <v>33734</v>
       </c>
       <c r="K31" s="5">
-        <v>80388</v>
+        <v>80392</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.99353610757498978</v>
+        <v>0.99358554461074511</v>
       </c>
       <c r="M31" s="5">
         <v>142260</v>
@@ -5764,14 +5764,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>72184</v>
+        <v>72190</v>
       </c>
       <c r="P31" s="5">
-        <v>142774</v>
+        <v>142780</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0036131027695769</v>
+        <v>1.0036552790664979</v>
       </c>
       <c r="R31" s="5">
         <v>79665</v>
@@ -5781,14 +5781,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>33846</v>
+        <v>33851</v>
       </c>
       <c r="U31" s="5">
-        <v>79782</v>
+        <v>79787</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>1.0014686499717567</v>
+        <v>1.0015314127910626</v>
       </c>
       <c r="W31" s="5">
         <v>81657</v>
@@ -5798,14 +5798,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>20678</v>
+        <v>20682</v>
       </c>
       <c r="Z31" s="5">
-        <v>80695</v>
+        <v>80699</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.9882190136791702</v>
+        <v>0.98826799906927754</v>
       </c>
       <c r="AB31" s="5">
         <v>144167</v>
@@ -5815,14 +5815,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>77280</v>
+        <v>77293</v>
       </c>
       <c r="AE31" s="5">
-        <v>144629</v>
+        <v>144642</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0032046168679378</v>
+        <v>1.0032947900698495</v>
       </c>
       <c r="AG31" s="5">
         <v>80917</v>
@@ -5832,14 +5832,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>35655</v>
+        <v>35664</v>
       </c>
       <c r="AJ31" s="5">
-        <v>81479</v>
+        <v>81488</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>1.0069453884844966</v>
+        <v>1.0070566135669885</v>
       </c>
       <c r="AL31" s="5">
         <v>83546</v>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="14"/>
-        <v>33674</v>
+        <v>33682</v>
       </c>
       <c r="AO31" s="5">
-        <v>82732</v>
+        <v>82740</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="15"/>
-        <v>0.99025686448184236</v>
+        <v>0.99035262011347047</v>
       </c>
       <c r="AQ31" s="5">
         <v>147023</v>
@@ -5866,14 +5866,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>69538</v>
+        <v>69557</v>
       </c>
       <c r="AT31" s="5">
-        <v>147351</v>
+        <v>147370</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="17"/>
-        <v>1.0022309434578263</v>
+        <v>1.0023601749386151</v>
       </c>
       <c r="AV31" s="5">
         <v>81694</v>
@@ -5883,14 +5883,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="18"/>
-        <v>33825</v>
+        <v>33834</v>
       </c>
       <c r="AY31" s="5">
-        <v>82330</v>
+        <v>82339</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="19"/>
-        <v>1.0077851494601806</v>
+        <v>1.0078953166695228</v>
       </c>
       <c r="BA31" s="5">
         <v>83957</v>
@@ -5900,14 +5900,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="20"/>
-        <v>32830</v>
+        <v>32839</v>
       </c>
       <c r="BD31" s="5">
-        <v>83387</v>
+        <v>83396</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="21"/>
-        <v>0.99321081029574665</v>
+        <v>0.99331800802791903</v>
       </c>
       <c r="BF31" s="5">
         <v>148810</v>
@@ -5917,14 +5917,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>78811</v>
+        <v>78834</v>
       </c>
       <c r="BI31" s="5">
-        <v>149399</v>
+        <v>149422</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>1.0039580673341846</v>
+        <v>1.0041126268395941</v>
       </c>
       <c r="BL31" s="9"/>
     </row>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>97873</v>
+        <v>97875</v>
       </c>
       <c r="F32" s="5">
-        <v>217271</v>
+        <v>217273</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.98942589244648049</v>
+        <v>0.98943500020492459</v>
       </c>
       <c r="H32" s="5">
         <v>225984</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>97773</v>
+        <v>97778</v>
       </c>
       <c r="K32" s="5">
-        <v>222091</v>
+        <v>222096</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98277311668082701</v>
+        <v>0.98279524214103653</v>
       </c>
       <c r="M32" s="5">
         <v>469379</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>251994</v>
+        <v>252006</v>
       </c>
       <c r="P32" s="5">
-        <v>466912</v>
+        <v>466924</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99474411935770457</v>
+        <v>0.99476968505195162</v>
       </c>
       <c r="R32" s="5">
         <v>220673</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>98822</v>
+        <v>98829</v>
       </c>
       <c r="U32" s="5">
-        <v>219225</v>
+        <v>219232</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.9934382547932914</v>
+        <v>0.99346997593724651</v>
       </c>
       <c r="W32" s="5">
         <v>228851</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>47511</v>
+        <v>47519</v>
       </c>
       <c r="Z32" s="5">
-        <v>222461</v>
+        <v>222469</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.97207790221585222</v>
+        <v>0.97211285945877446</v>
       </c>
       <c r="AB32" s="5">
         <v>476427</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>270014</v>
+        <v>270037</v>
       </c>
       <c r="AE32" s="5">
-        <v>472716</v>
+        <v>472739</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99221076891108184</v>
+        <v>0.99225904493238204</v>
       </c>
       <c r="AG32" s="5">
         <v>224544</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>99837</v>
+        <v>99846</v>
       </c>
       <c r="AJ32" s="5">
-        <v>222971</v>
+        <v>222980</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99299469146358843</v>
+        <v>0.99303477269488383</v>
       </c>
       <c r="AL32" s="5">
         <v>231787</v>
@@ -6062,14 +6062,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="14"/>
-        <v>96370</v>
+        <v>96381</v>
       </c>
       <c r="AO32" s="5">
-        <v>227015</v>
+        <v>227026</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="15"/>
-        <v>0.97941213269078942</v>
+        <v>0.97945959005466221</v>
       </c>
       <c r="AQ32" s="5">
         <v>484390</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>236293</v>
+        <v>236323</v>
       </c>
       <c r="AT32" s="5">
-        <v>481460</v>
+        <v>481490</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="17"/>
-        <v>0.99395115506100451</v>
+        <v>0.99401308862693283</v>
       </c>
       <c r="AV32" s="5">
         <v>227629</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="18"/>
-        <v>94086</v>
+        <v>94098</v>
       </c>
       <c r="AY32" s="5">
-        <v>226713</v>
+        <v>226725</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="19"/>
-        <v>0.99597590816635839</v>
+        <v>0.99602862552662441</v>
       </c>
       <c r="BA32" s="5">
         <v>234918</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="20"/>
-        <v>95001</v>
+        <v>95015</v>
       </c>
       <c r="BD32" s="5">
-        <v>231466</v>
+        <v>231480</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="21"/>
-        <v>0.98530551085910834</v>
+        <v>0.98536510612213624</v>
       </c>
       <c r="BF32" s="5">
         <v>492680</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>270400</v>
+        <v>270436</v>
       </c>
       <c r="BI32" s="5">
-        <v>490752</v>
+        <v>490788</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.99608670942599664</v>
+        <v>0.99615977916700493</v>
       </c>
       <c r="BL32" s="9"/>
     </row>
@@ -6156,14 +6156,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>93957</v>
+        <v>93959</v>
       </c>
       <c r="F33" s="5">
-        <v>662167</v>
+        <v>662169</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.99812333813678378</v>
+        <v>0.99812635285463636</v>
       </c>
       <c r="H33" s="5">
         <v>674602</v>
@@ -6173,14 +6173,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>92452</v>
+        <v>92456</v>
       </c>
       <c r="K33" s="5">
-        <v>670110</v>
+        <v>670114</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99334125899419212</v>
+        <v>0.993347188416281</v>
       </c>
       <c r="M33" s="5">
         <v>1077651</v>
@@ -6190,14 +6190,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>180272</v>
+        <v>180278</v>
       </c>
       <c r="P33" s="5">
-        <v>1078243</v>
+        <v>1078249</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0005493429691059</v>
+        <v>1.0005549106343334</v>
       </c>
       <c r="R33" s="5">
         <v>670885</v>
@@ -6207,14 +6207,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>98757</v>
+        <v>98761</v>
       </c>
       <c r="U33" s="5">
-        <v>671012</v>
+        <v>671016</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>1.0001893021903903</v>
+        <v>1.0001952644641035</v>
       </c>
       <c r="W33" s="5">
         <v>679851</v>
@@ -6224,14 +6224,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>75110</v>
+        <v>75115</v>
       </c>
       <c r="Z33" s="5">
-        <v>677895</v>
+        <v>677900</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.99712289898816064</v>
+        <v>0.99713025354084939</v>
       </c>
       <c r="AB33" s="5">
         <v>1091619</v>
@@ -6241,14 +6241,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>205451</v>
+        <v>205461</v>
       </c>
       <c r="AE33" s="5">
-        <v>1092093</v>
+        <v>1092103</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0004342174330054</v>
+        <v>1.0004433781383431</v>
       </c>
       <c r="AG33" s="5">
         <v>681949</v>
@@ -6258,14 +6258,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>121284</v>
+        <v>121291</v>
       </c>
       <c r="AJ33" s="5">
-        <v>682573</v>
+        <v>682580</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>1.0009150244373113</v>
+        <v>1.0009252891345248</v>
       </c>
       <c r="AL33" s="5">
         <v>691548</v>
@@ -6275,14 +6275,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="14"/>
-        <v>90820</v>
+        <v>90827</v>
       </c>
       <c r="AO33" s="5">
-        <v>689010</v>
+        <v>689017</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="15"/>
-        <v>0.99632997275677171</v>
+        <v>0.99634009497533071</v>
       </c>
       <c r="AQ33" s="5">
         <v>1107071</v>
@@ -6292,14 +6292,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="16"/>
-        <v>167906</v>
+        <v>167913</v>
       </c>
       <c r="AT33" s="5">
-        <v>1110269</v>
+        <v>1110276</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="17"/>
-        <v>1.0028887036152152</v>
+        <v>1.0028950266062429</v>
       </c>
       <c r="AV33" s="5">
         <v>697202</v>
@@ -6309,14 +6309,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="18"/>
-        <v>89923</v>
+        <v>89930</v>
       </c>
       <c r="AY33" s="5">
-        <v>698908</v>
+        <v>698915</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="19"/>
-        <v>1.0024469235601734</v>
+        <v>1.0024569636920146</v>
       </c>
       <c r="BA33" s="5">
         <v>707985</v>
@@ -6326,14 +6326,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="20"/>
-        <v>90166</v>
+        <v>90172</v>
       </c>
       <c r="BD33" s="5">
-        <v>709263</v>
+        <v>709269</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="21"/>
-        <v>1.0018051229898939</v>
+        <v>1.001813597745715</v>
       </c>
       <c r="BF33" s="5">
         <v>1132408</v>
@@ -6343,14 +6343,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>207746</v>
+        <v>207764</v>
       </c>
       <c r="BI33" s="5">
-        <v>1134976</v>
+        <v>1134994</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>1.0022677338909651</v>
+        <v>1.0022836292219766</v>
       </c>
       <c r="BL33" s="9"/>
     </row>
@@ -6677,14 +6677,14 @@
       </c>
       <c r="AN35" s="3">
         <f t="shared" ref="AN35:AN47" si="38">AO35-AM35</f>
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="AO35" s="5">
-        <v>12098</v>
+        <v>12099</v>
       </c>
       <c r="AP35" s="4">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.99334920765251666</v>
+        <v>0.99343131620001646</v>
       </c>
       <c r="AQ35" s="5">
         <v>14849</v>
@@ -6694,14 +6694,14 @@
       </c>
       <c r="AS35" s="3">
         <f t="shared" ref="AS35:AS47" si="40">AT35-AR35</f>
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="AT35" s="5">
-        <v>14860</v>
+        <v>14861</v>
       </c>
       <c r="AU35" s="4">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>1.0007407906256314</v>
+        <v>1.0008081352279614</v>
       </c>
       <c r="AV35" s="5">
         <v>12178</v>
@@ -6711,14 +6711,14 @@
       </c>
       <c r="AX35" s="3">
         <f t="shared" ref="AX35:AX47" si="42">AY35-AW35</f>
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="AY35" s="5">
-        <v>12193</v>
+        <v>12194</v>
       </c>
       <c r="AZ35" s="4">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>1.0012317293480046</v>
+        <v>1.0013138446378715</v>
       </c>
       <c r="BA35" s="5">
         <v>12308</v>
@@ -6728,14 +6728,14 @@
       </c>
       <c r="BC35" s="3">
         <f t="shared" ref="BC35:BC47" si="44">BD35-BB35</f>
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="BD35" s="5">
-        <v>12250</v>
+        <v>12251</v>
       </c>
       <c r="BE35" s="4">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.99528761780955477</v>
+        <v>0.99536886577835559</v>
       </c>
       <c r="BF35" s="5">
         <v>15013</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="46">BI35-BG35</f>
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="BI35" s="5">
-        <v>14995</v>
+        <v>14996</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.99880103909944717</v>
+        <v>0.9988676480383667</v>
       </c>
       <c r="BL35" s="9"/>
     </row>
@@ -6771,14 +6771,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="24"/>
-        <v>250195</v>
+        <v>250212</v>
       </c>
       <c r="F36" s="5">
-        <v>887288</v>
+        <v>887305</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="25"/>
-        <v>0.99152726094293031</v>
+        <v>0.99154625811570396</v>
       </c>
       <c r="H36" s="5">
         <v>910737</v>
@@ -6788,14 +6788,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="26"/>
-        <v>242715</v>
+        <v>242734</v>
       </c>
       <c r="K36" s="5">
-        <v>898415</v>
+        <v>898434</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="27"/>
-        <v>0.98647029823099319</v>
+        <v>0.98649116045576279</v>
       </c>
       <c r="M36" s="5">
         <v>1579599</v>
@@ -6805,14 +6805,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="28"/>
-        <v>490123</v>
+        <v>490161</v>
       </c>
       <c r="P36" s="5">
-        <v>1571312</v>
+        <v>1571350</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="29"/>
-        <v>0.99475373180155213</v>
+        <v>0.99477778854000287</v>
       </c>
       <c r="R36" s="5">
         <v>901122</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="30"/>
-        <v>252314</v>
+        <v>252339</v>
       </c>
       <c r="U36" s="5">
-        <v>897758</v>
+        <v>897783</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="31"/>
-        <v>0.99626687618324705</v>
+        <v>0.99629461937451314</v>
       </c>
       <c r="W36" s="5">
         <v>923866</v>
@@ -6839,14 +6839,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="32"/>
-        <v>177930</v>
+        <v>177959</v>
       </c>
       <c r="Z36" s="5">
-        <v>907159</v>
+        <v>907188</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98191620862765816</v>
+        <v>0.98194759846124868</v>
       </c>
       <c r="AB36" s="5">
         <v>1592928</v>
@@ -6856,14 +6856,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="34"/>
-        <v>534714</v>
+        <v>534768</v>
       </c>
       <c r="AE36" s="5">
-        <v>1588340</v>
+        <v>1588394</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99711976938066249</v>
+        <v>0.99715366921794335</v>
       </c>
       <c r="AG36" s="5">
         <v>914936</v>
@@ -6873,14 +6873,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="36"/>
-        <v>259767</v>
+        <v>259802</v>
       </c>
       <c r="AJ36" s="5">
-        <v>912113</v>
+        <v>912148</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99691453828464505</v>
+        <v>0.99695279232645784</v>
       </c>
       <c r="AL36" s="5">
         <v>934551</v>
@@ -6890,14 +6890,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="38"/>
-        <v>238526</v>
+        <v>238568</v>
       </c>
       <c r="AO36" s="5">
-        <v>922790</v>
+        <v>922832</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="39"/>
-        <v>0.98741534704901068</v>
+        <v>0.98746028841657651</v>
       </c>
       <c r="AQ36" s="5">
         <v>1610673</v>
@@ -6907,14 +6907,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="40"/>
-        <v>455259</v>
+        <v>455343</v>
       </c>
       <c r="AT36" s="5">
-        <v>1612932</v>
+        <v>1613016</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="41"/>
-        <v>1.0014025193195639</v>
+        <v>1.0014546714323764</v>
       </c>
       <c r="AV36" s="5">
         <v>933166</v>
@@ -6924,14 +6924,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="42"/>
-        <v>234068</v>
+        <v>234116</v>
       </c>
       <c r="AY36" s="5">
-        <v>933262</v>
+        <v>933310</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="43"/>
-        <v>1.0001028755869803</v>
+        <v>1.0001543133804704</v>
       </c>
       <c r="BA36" s="5">
         <v>952259</v>
@@ -6941,14 +6941,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="44"/>
-        <v>234347</v>
+        <v>234400</v>
       </c>
       <c r="BD36" s="5">
-        <v>945345</v>
+        <v>945398</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="45"/>
-        <v>0.99273937027636394</v>
+        <v>0.99279502740325898</v>
       </c>
       <c r="BF36" s="5">
         <v>1640364</v>
@@ -6958,14 +6958,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="46"/>
-        <v>523065</v>
+        <v>523201</v>
       </c>
       <c r="BI36" s="5">
-        <v>1642101</v>
+        <v>1642237</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="47"/>
-        <v>1.0010589113148058</v>
+        <v>1.0011418197424473</v>
       </c>
       <c r="BL36" s="9"/>
     </row>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="24"/>
-        <v>284594</v>
+        <v>284620</v>
       </c>
       <c r="F37" s="5">
-        <v>701011</v>
+        <v>701037</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="25"/>
-        <v>0.98762598725827488</v>
+        <v>0.98766261760454443</v>
       </c>
       <c r="H37" s="5">
         <v>717455</v>
@@ -7001,14 +7001,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="26"/>
-        <v>273428</v>
+        <v>273455</v>
       </c>
       <c r="K37" s="5">
-        <v>706609</v>
+        <v>706636</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="27"/>
-        <v>0.98488267556850251</v>
+        <v>0.98492030859078272</v>
       </c>
       <c r="M37" s="5">
         <v>885615</v>
@@ -7018,14 +7018,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="28"/>
-        <v>352396</v>
+        <v>352440</v>
       </c>
       <c r="P37" s="5">
-        <v>879410</v>
+        <v>879454</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="29"/>
-        <v>0.99299356944044537</v>
+        <v>0.99304325242910296</v>
       </c>
       <c r="R37" s="5">
         <v>713906</v>
@@ -7035,14 +7035,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="30"/>
-        <v>285549</v>
+        <v>285579</v>
       </c>
       <c r="U37" s="5">
-        <v>707787</v>
+        <v>707817</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="31"/>
-        <v>0.99142884357324357</v>
+        <v>0.99147086591231903</v>
       </c>
       <c r="W37" s="5">
         <v>721933</v>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="32"/>
-        <v>129108</v>
+        <v>129143</v>
       </c>
       <c r="Z37" s="5">
-        <v>709731</v>
+        <v>709766</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98309815453788651</v>
+        <v>0.98314663549110515</v>
       </c>
       <c r="AB37" s="5">
         <v>896229</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="34"/>
-        <v>388020</v>
+        <v>388070</v>
       </c>
       <c r="AE37" s="5">
-        <v>884835</v>
+        <v>884885</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="35"/>
-        <v>0.98728673140458523</v>
+        <v>0.98734252071736128</v>
       </c>
       <c r="AG37" s="5">
         <v>721282</v>
@@ -7086,14 +7086,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="36"/>
-        <v>283246</v>
+        <v>283287</v>
       </c>
       <c r="AJ37" s="5">
-        <v>712211</v>
+        <v>712252</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="37"/>
-        <v>0.9874237815445277</v>
+        <v>0.98748062477643972</v>
       </c>
       <c r="AL37" s="5">
         <v>727480</v>
@@ -7103,14 +7103,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="38"/>
-        <v>265700</v>
+        <v>265749</v>
       </c>
       <c r="AO37" s="5">
-        <v>718168</v>
+        <v>718217</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="39"/>
-        <v>0.98719964810029137</v>
+        <v>0.98726700390388744</v>
       </c>
       <c r="AQ37" s="5">
         <v>903787</v>
@@ -7120,14 +7120,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="40"/>
-        <v>339045</v>
+        <v>339116</v>
       </c>
       <c r="AT37" s="5">
-        <v>897419</v>
+        <v>897490</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99295409205930163</v>
+        <v>0.99303265039218314</v>
       </c>
       <c r="AV37" s="5">
         <v>732294</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="42"/>
-        <v>269998</v>
+        <v>270061</v>
       </c>
       <c r="AY37" s="5">
-        <v>726370</v>
+        <v>726433</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="43"/>
-        <v>0.99191035294567487</v>
+        <v>0.99199638396600276</v>
       </c>
       <c r="BA37" s="5">
         <v>740889</v>
@@ -7154,14 +7154,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="44"/>
-        <v>267374</v>
+        <v>267444</v>
       </c>
       <c r="BD37" s="5">
-        <v>731574</v>
+        <v>731644</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="45"/>
-        <v>0.98742726643262346</v>
+        <v>0.98752174752223343</v>
       </c>
       <c r="BF37" s="5">
         <v>918028</v>
@@ -7171,14 +7171,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="46"/>
-        <v>377986</v>
+        <v>378099</v>
       </c>
       <c r="BI37" s="5">
-        <v>910361</v>
+        <v>910474</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="47"/>
-        <v>0.9916484028809579</v>
+        <v>0.99177149280849819</v>
       </c>
       <c r="BL37" s="9"/>
     </row>
@@ -7197,14 +7197,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="24"/>
-        <v>9276</v>
+        <v>9277</v>
       </c>
       <c r="F38" s="5">
-        <v>24449</v>
+        <v>24450</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="25"/>
-        <v>1.0038595770888934</v>
+        <v>1.0039006364196263</v>
       </c>
       <c r="H38" s="5">
         <v>24747</v>
@@ -7214,14 +7214,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="26"/>
-        <v>8856</v>
+        <v>8857</v>
       </c>
       <c r="K38" s="5">
-        <v>24698</v>
+        <v>24699</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="27"/>
-        <v>0.99801996201559784</v>
+        <v>0.99806037095405509</v>
       </c>
       <c r="M38" s="5">
         <v>37604</v>
@@ -7231,14 +7231,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="28"/>
-        <v>13791</v>
+        <v>13795</v>
       </c>
       <c r="P38" s="5">
-        <v>37833</v>
+        <v>37837</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="29"/>
-        <v>1.0060897776832252</v>
+        <v>1.0061961493458143</v>
       </c>
       <c r="R38" s="5">
         <v>24596</v>
@@ -7248,14 +7248,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="30"/>
-        <v>9384</v>
+        <v>9387</v>
       </c>
       <c r="U38" s="5">
-        <v>24785</v>
+        <v>24788</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="31"/>
-        <v>1.0076841762888276</v>
+        <v>1.0078061473410311</v>
       </c>
       <c r="W38" s="5">
         <v>25148</v>
@@ -7265,14 +7265,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="32"/>
-        <v>6023</v>
+        <v>6025</v>
       </c>
       <c r="Z38" s="5">
-        <v>24975</v>
+        <v>24977</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="33"/>
-        <v>0.99312072530618734</v>
+        <v>0.9932002544933991</v>
       </c>
       <c r="AB38" s="5">
         <v>38035</v>
@@ -7282,14 +7282,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="34"/>
-        <v>14772</v>
+        <v>14775</v>
       </c>
       <c r="AE38" s="5">
-        <v>38240</v>
+        <v>38243</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0053897725778889</v>
+        <v>1.0054686472985408</v>
       </c>
       <c r="AG38" s="5">
         <v>24962</v>
@@ -7299,14 +7299,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="36"/>
-        <v>9217</v>
+        <v>9219</v>
       </c>
       <c r="AJ38" s="5">
-        <v>25188</v>
+        <v>25190</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="37"/>
-        <v>1.009053761717811</v>
+        <v>1.0091338835029244</v>
       </c>
       <c r="AL38" s="5">
         <v>25436</v>
@@ -7316,14 +7316,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="38"/>
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="AO38" s="5">
-        <v>25471</v>
+        <v>25473</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="39"/>
-        <v>1.0013760025161189</v>
+        <v>1.0014546312313257</v>
       </c>
       <c r="AQ38" s="5">
         <v>38569</v>
@@ -7333,14 +7333,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="40"/>
-        <v>13211</v>
+        <v>13215</v>
       </c>
       <c r="AT38" s="5">
-        <v>38966</v>
+        <v>38970</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0102932406855247</v>
+        <v>1.010396950919132</v>
       </c>
       <c r="AV38" s="5">
         <v>25488</v>
@@ -7350,14 +7350,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="42"/>
-        <v>8640</v>
+        <v>8642</v>
       </c>
       <c r="AY38" s="5">
-        <v>25668</v>
+        <v>25670</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="43"/>
-        <v>1.0070621468926553</v>
+        <v>1.0071406151914626</v>
       </c>
       <c r="BA38" s="5">
         <v>25933</v>
@@ -7367,14 +7367,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="44"/>
-        <v>8616</v>
+        <v>8618</v>
       </c>
       <c r="BD38" s="5">
-        <v>25948</v>
+        <v>25950</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="45"/>
-        <v>1.0005784136042879</v>
+        <v>1.000655535418193</v>
       </c>
       <c r="BF38" s="5">
         <v>39379</v>
@@ -7384,14 +7384,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="46"/>
-        <v>15265</v>
+        <v>15272</v>
       </c>
       <c r="BI38" s="5">
-        <v>39604</v>
+        <v>39611</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="47"/>
-        <v>1.0057137052743848</v>
+        <v>1.0058914649940323</v>
       </c>
       <c r="BL38" s="9"/>
     </row>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="24"/>
-        <v>112615</v>
+        <v>112625</v>
       </c>
       <c r="F40" s="5">
-        <v>289345</v>
+        <v>289355</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="25"/>
-        <v>0.99108402866263856</v>
+        <v>0.99111828133777247</v>
       </c>
       <c r="H40" s="5">
         <v>293812</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="26"/>
-        <v>110833</v>
+        <v>110842</v>
       </c>
       <c r="K40" s="5">
-        <v>290947</v>
+        <v>290956</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="27"/>
-        <v>0.9902488666221938</v>
+        <v>0.99027949845479424</v>
       </c>
       <c r="M40" s="5">
         <v>351809</v>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="28"/>
-        <v>138089</v>
+        <v>138104</v>
       </c>
       <c r="P40" s="5">
-        <v>349825</v>
+        <v>349840</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="29"/>
-        <v>0.99436057633545472</v>
+        <v>0.99440321310711211</v>
       </c>
       <c r="R40" s="5">
         <v>293831</v>
@@ -7674,14 +7674,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="30"/>
-        <v>115536</v>
+        <v>115550</v>
       </c>
       <c r="U40" s="5">
-        <v>292940</v>
+        <v>292954</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="31"/>
-        <v>0.99696764466649201</v>
+        <v>0.9970152911027087</v>
       </c>
       <c r="W40" s="5">
         <v>297227</v>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="32"/>
-        <v>66844</v>
+        <v>66858</v>
       </c>
       <c r="Z40" s="5">
-        <v>294389</v>
+        <v>294403</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="33"/>
-        <v>0.99045174227105881</v>
+        <v>0.99049884431764279</v>
       </c>
       <c r="AB40" s="5">
         <v>355500</v>
@@ -7708,14 +7708,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="34"/>
-        <v>143021</v>
+        <v>143038</v>
       </c>
       <c r="AE40" s="5">
-        <v>353491</v>
+        <v>353508</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="35"/>
-        <v>0.99434880450070329</v>
+        <v>0.99439662447257382</v>
       </c>
       <c r="AG40" s="5">
         <v>298328</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="36"/>
-        <v>116524</v>
+        <v>116541</v>
       </c>
       <c r="AJ40" s="5">
-        <v>296165</v>
+        <v>296182</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="37"/>
-        <v>0.99274959105414173</v>
+        <v>0.99280657531307825</v>
       </c>
       <c r="AL40" s="5">
         <v>299711</v>
@@ -7742,14 +7742,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="38"/>
-        <v>111325</v>
+        <v>111343</v>
       </c>
       <c r="AO40" s="5">
-        <v>297480</v>
+        <v>297498</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99255616243648048</v>
+        <v>0.99261622029221486</v>
       </c>
       <c r="AQ40" s="5">
         <v>357015</v>
@@ -7759,14 +7759,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="40"/>
-        <v>136720</v>
+        <v>136747</v>
       </c>
       <c r="AT40" s="5">
-        <v>355977</v>
+        <v>356004</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99709255913617079</v>
+        <v>0.99716818621066339</v>
       </c>
       <c r="AV40" s="5">
         <v>300800</v>
@@ -7776,14 +7776,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="42"/>
-        <v>112865</v>
+        <v>112888</v>
       </c>
       <c r="AY40" s="5">
-        <v>299492</v>
+        <v>299515</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="43"/>
-        <v>0.99565159574468087</v>
+        <v>0.99572805851063828</v>
       </c>
       <c r="BA40" s="5">
         <v>303731</v>
@@ -7793,14 +7793,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="44"/>
-        <v>110903</v>
+        <v>110929</v>
       </c>
       <c r="BD40" s="5">
-        <v>300947</v>
+        <v>300973</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="45"/>
-        <v>0.99083399455439192</v>
+        <v>0.99091959661674311</v>
       </c>
       <c r="BF40" s="5">
         <v>361393</v>
@@ -7810,14 +7810,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="46"/>
-        <v>149393</v>
+        <v>149441</v>
       </c>
       <c r="BI40" s="5">
-        <v>359378</v>
+        <v>359426</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="47"/>
-        <v>0.99442435243626748</v>
+        <v>0.99455717183232661</v>
       </c>
       <c r="BL40" s="9"/>
     </row>
@@ -7836,14 +7836,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="24"/>
-        <v>362832</v>
+        <v>362868</v>
       </c>
       <c r="F41" s="5">
-        <v>945146</v>
+        <v>945182</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="25"/>
-        <v>0.99237511654669008</v>
+        <v>0.99241291547320054</v>
       </c>
       <c r="H41" s="5">
         <v>959446</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="26"/>
-        <v>364375</v>
+        <v>364411</v>
       </c>
       <c r="K41" s="5">
-        <v>948907</v>
+        <v>948943</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="27"/>
-        <v>0.98901553604892822</v>
+        <v>0.98905305770204888</v>
       </c>
       <c r="M41" s="5">
         <v>1062442</v>
@@ -7870,14 +7870,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="28"/>
-        <v>401997</v>
+        <v>402038</v>
       </c>
       <c r="P41" s="5">
-        <v>1053568</v>
+        <v>1053609</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="29"/>
-        <v>0.99164754405416955</v>
+        <v>0.99168613439604236</v>
       </c>
       <c r="R41" s="5">
         <v>959218</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="30"/>
-        <v>375475</v>
+        <v>375513</v>
       </c>
       <c r="U41" s="5">
-        <v>952246</v>
+        <v>952284</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="31"/>
-        <v>0.99273157926561006</v>
+        <v>0.99277119486915388</v>
       </c>
       <c r="W41" s="5">
         <v>961845</v>
@@ -7904,14 +7904,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="32"/>
-        <v>151898</v>
+        <v>151946</v>
       </c>
       <c r="Z41" s="5">
-        <v>951505</v>
+        <v>951553</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="33"/>
-        <v>0.9892498271551029</v>
+        <v>0.98929973124567883</v>
       </c>
       <c r="AB41" s="5">
         <v>1065577</v>
@@ -7921,14 +7921,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="34"/>
-        <v>434566</v>
+        <v>434615</v>
       </c>
       <c r="AE41" s="5">
-        <v>1056956</v>
+        <v>1057005</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="35"/>
-        <v>0.99190954759721728</v>
+        <v>0.99195553207323361</v>
       </c>
       <c r="AG41" s="5">
         <v>963364</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="36"/>
-        <v>374521</v>
+        <v>374570</v>
       </c>
       <c r="AJ41" s="5">
-        <v>957414</v>
+        <v>957463</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99382372602671476</v>
+        <v>0.99387458945943585</v>
       </c>
       <c r="AL41" s="5">
         <v>968650</v>
@@ -7955,14 +7955,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="38"/>
-        <v>342463</v>
+        <v>342515</v>
       </c>
       <c r="AO41" s="5">
-        <v>959982</v>
+        <v>960034</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="39"/>
-        <v>0.99105146337686467</v>
+        <v>0.99110514633768643</v>
       </c>
       <c r="AQ41" s="5">
         <v>1071657</v>
@@ -7972,14 +7972,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="40"/>
-        <v>363910</v>
+        <v>363971</v>
       </c>
       <c r="AT41" s="5">
-        <v>1065141</v>
+        <v>1065202</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="41"/>
-        <v>0.99391969632074439</v>
+        <v>0.99397661751847843</v>
       </c>
       <c r="AV41" s="5">
         <v>970535</v>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="42"/>
-        <v>340807</v>
+        <v>340861</v>
       </c>
       <c r="AY41" s="5">
-        <v>965225</v>
+        <v>965279</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="43"/>
-        <v>0.99452879082155721</v>
+        <v>0.99458443023693122</v>
       </c>
       <c r="BA41" s="5">
         <v>973311</v>
@@ -8006,14 +8006,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="44"/>
-        <v>336638</v>
+        <v>336714</v>
       </c>
       <c r="BD41" s="5">
-        <v>970143</v>
+        <v>970219</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="45"/>
-        <v>0.9967451307958094</v>
+        <v>0.99682321477924318</v>
       </c>
       <c r="BF41" s="5">
         <v>1078355</v>
@@ -8023,14 +8023,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="46"/>
-        <v>404470</v>
+        <v>404563</v>
       </c>
       <c r="BI41" s="5">
-        <v>1076056</v>
+        <v>1076149</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99786804901910786</v>
+        <v>0.99795429149027914</v>
       </c>
       <c r="BL41" s="9"/>
     </row>
@@ -8083,14 +8083,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="28"/>
-        <v>9353</v>
+        <v>9354</v>
       </c>
       <c r="P42" s="5">
-        <v>21024</v>
+        <v>21025</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="29"/>
-        <v>0.99193205944798302</v>
+        <v>0.99197924038688368</v>
       </c>
       <c r="R42" s="5">
         <v>19210</v>
@@ -8236,14 +8236,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="46"/>
-        <v>9813</v>
+        <v>9814</v>
       </c>
       <c r="BI42" s="5">
-        <v>21631</v>
+        <v>21632</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="47"/>
-        <v>0.99261196769456683</v>
+        <v>0.9926578560939795</v>
       </c>
       <c r="BL42" s="9"/>
     </row>
@@ -8262,14 +8262,14 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="24"/>
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="F43" s="5">
-        <v>3671</v>
+        <v>3672</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="25"/>
-        <v>1.0005451076587626</v>
+        <v>1.0008176614881439</v>
       </c>
       <c r="H43" s="5">
         <v>3731</v>
@@ -8279,14 +8279,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="26"/>
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="K43" s="5">
-        <v>3710</v>
+        <v>3711</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="27"/>
-        <v>0.99437148217636018</v>
+        <v>0.99463950683462876</v>
       </c>
       <c r="M43" s="5">
         <v>4602</v>
@@ -8296,14 +8296,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="28"/>
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="P43" s="5">
-        <v>4600</v>
+        <v>4601</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="29"/>
-        <v>0.99956540634506741</v>
+        <v>0.9997827031725337</v>
       </c>
       <c r="R43" s="5">
         <v>3744</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="30"/>
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="U43" s="5">
-        <v>3742</v>
+        <v>3743</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="31"/>
-        <v>0.99946581196581197</v>
+        <v>0.99973290598290598</v>
       </c>
       <c r="W43" s="5">
         <v>3795</v>
@@ -8330,14 +8330,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="32"/>
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="Z43" s="5">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="33"/>
-        <v>0.99235836627140972</v>
+        <v>0.99262187088274045</v>
       </c>
       <c r="AB43" s="5">
         <v>4656</v>
@@ -8347,14 +8347,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="34"/>
-        <v>2788</v>
+        <v>2790</v>
       </c>
       <c r="AE43" s="5">
-        <v>4641</v>
+        <v>4643</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="35"/>
-        <v>0.99677835051546393</v>
+        <v>0.99720790378006874</v>
       </c>
       <c r="AG43" s="5">
         <v>3765</v>
@@ -8364,14 +8364,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="36"/>
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3774</v>
+        <v>3776</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="37"/>
-        <v>1.0023904382470119</v>
+        <v>1.002921646746348</v>
       </c>
       <c r="AL43" s="5">
         <v>3815</v>
@@ -8381,14 +8381,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="38"/>
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="AO43" s="5">
-        <v>3817</v>
+        <v>3819</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="39"/>
-        <v>1.0005242463958059</v>
+        <v>1.0010484927916121</v>
       </c>
       <c r="AQ43" s="5">
         <v>4752</v>
@@ -8398,14 +8398,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="40"/>
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="AT43" s="5">
-        <v>4772</v>
+        <v>4774</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="41"/>
-        <v>1.0042087542087541</v>
+        <v>1.0046296296296295</v>
       </c>
       <c r="AV43" s="5">
         <v>3858</v>
@@ -8415,14 +8415,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="42"/>
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="AY43" s="5">
-        <v>3836</v>
+        <v>3838</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="43"/>
-        <v>0.99429756350440646</v>
+        <v>0.99481596682218765</v>
       </c>
       <c r="BA43" s="5">
         <v>3902</v>
@@ -8432,14 +8432,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="44"/>
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="BD43" s="5">
-        <v>3868</v>
+        <v>3871</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="45"/>
-        <v>0.99128651973347004</v>
+        <v>0.99205535622757557</v>
       </c>
       <c r="BF43" s="5">
         <v>4852</v>
@@ -8449,14 +8449,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="46"/>
-        <v>2842</v>
+        <v>2844</v>
       </c>
       <c r="BI43" s="5">
-        <v>4824</v>
+        <v>4826</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="47"/>
-        <v>0.99422918384171477</v>
+        <v>0.99464138499587795</v>
       </c>
       <c r="BL43" s="9"/>
     </row>
@@ -8475,14 +8475,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="24"/>
-        <v>174709</v>
+        <v>174714</v>
       </c>
       <c r="F44" s="5">
-        <v>359919</v>
+        <v>359924</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="25"/>
-        <v>0.98954965357967672</v>
+        <v>0.98956340041790392</v>
       </c>
       <c r="H44" s="5">
         <v>368428</v>
@@ -8492,14 +8492,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="26"/>
-        <v>171134</v>
+        <v>171138</v>
       </c>
       <c r="K44" s="5">
-        <v>362641</v>
+        <v>362645</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="27"/>
-        <v>0.98429272476576157</v>
+        <v>0.98430358170388788</v>
       </c>
       <c r="M44" s="5">
         <v>437654</v>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="28"/>
-        <v>205949</v>
+        <v>205959</v>
       </c>
       <c r="P44" s="5">
-        <v>431490</v>
+        <v>431500</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="29"/>
-        <v>0.98591581477605594</v>
+        <v>0.98593866387602991</v>
       </c>
       <c r="R44" s="5">
         <v>368991</v>
@@ -8526,14 +8526,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="30"/>
-        <v>177571</v>
+        <v>177577</v>
       </c>
       <c r="U44" s="5">
-        <v>365008</v>
+        <v>365014</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="31"/>
-        <v>0.98920569878398124</v>
+        <v>0.9892219593431818</v>
       </c>
       <c r="W44" s="5">
         <v>375659</v>
@@ -8543,14 +8543,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="32"/>
-        <v>79659</v>
+        <v>79668</v>
       </c>
       <c r="Z44" s="5">
-        <v>365158</v>
+        <v>365167</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="33"/>
-        <v>0.97204645702618597</v>
+        <v>0.97207041492417323</v>
       </c>
       <c r="AB44" s="5">
         <v>443838</v>
@@ -8560,14 +8560,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="34"/>
-        <v>217453</v>
+        <v>217469</v>
       </c>
       <c r="AE44" s="5">
-        <v>434615</v>
+        <v>434631</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="35"/>
-        <v>0.97921989554747457</v>
+        <v>0.97925594473659305</v>
       </c>
       <c r="AG44" s="5">
         <v>373881</v>
@@ -8577,14 +8577,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="36"/>
-        <v>174068</v>
+        <v>174081</v>
       </c>
       <c r="AJ44" s="5">
-        <v>367189</v>
+        <v>367202</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="37"/>
-        <v>0.98210125681700866</v>
+        <v>0.98213602723861337</v>
       </c>
       <c r="AL44" s="5">
         <v>377474</v>
@@ -8594,14 +8594,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="38"/>
-        <v>166977</v>
+        <v>166990</v>
       </c>
       <c r="AO44" s="5">
-        <v>370473</v>
+        <v>370486</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="39"/>
-        <v>0.98145302722836536</v>
+        <v>0.98148746668644726</v>
       </c>
       <c r="AQ44" s="5">
         <v>447335</v>
@@ -8611,14 +8611,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="40"/>
-        <v>201727</v>
+        <v>201748</v>
       </c>
       <c r="AT44" s="5">
-        <v>441364</v>
+        <v>441385</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="41"/>
-        <v>0.98665206165401764</v>
+        <v>0.98669900633753227</v>
       </c>
       <c r="AV44" s="5">
         <v>379419</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="42"/>
-        <v>167097</v>
+        <v>167117</v>
       </c>
       <c r="AY44" s="5">
-        <v>374589</v>
+        <v>374609</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="43"/>
-        <v>0.98727001019980554</v>
+        <v>0.9873227223728912</v>
       </c>
       <c r="BA44" s="5">
         <v>384239</v>
@@ -8645,14 +8645,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="44"/>
-        <v>165879</v>
+        <v>165902</v>
       </c>
       <c r="BD44" s="5">
-        <v>377539</v>
+        <v>377562</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="45"/>
-        <v>0.98256293608925693</v>
+        <v>0.98262279466686098</v>
       </c>
       <c r="BF44" s="5">
         <v>454173</v>
@@ -8662,14 +8662,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="46"/>
-        <v>219146</v>
+        <v>219174</v>
       </c>
       <c r="BI44" s="5">
-        <v>449028</v>
+        <v>449056</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="47"/>
-        <v>0.98867171760540584</v>
+        <v>0.98873336812183898</v>
       </c>
       <c r="BL44" s="9"/>
     </row>
@@ -8688,14 +8688,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="24"/>
-        <v>126127</v>
+        <v>126135</v>
       </c>
       <c r="F45" s="5">
-        <v>262636</v>
+        <v>262644</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="25"/>
-        <v>0.98504999587430897</v>
+        <v>0.9850800009001508</v>
       </c>
       <c r="H45" s="5">
         <v>269495</v>
@@ -8705,14 +8705,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="26"/>
-        <v>123625</v>
+        <v>123633</v>
       </c>
       <c r="K45" s="5">
-        <v>263977</v>
+        <v>263985</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="27"/>
-        <v>0.97952466650587211</v>
+        <v>0.97955435165773019</v>
       </c>
       <c r="M45" s="5">
         <v>320759</v>
@@ -8722,14 +8722,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="28"/>
-        <v>152049</v>
+        <v>152060</v>
       </c>
       <c r="P45" s="5">
-        <v>315256</v>
+        <v>315267</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="29"/>
-        <v>0.98284381732079229</v>
+        <v>0.98287811098051814</v>
       </c>
       <c r="R45" s="5">
         <v>267358</v>
@@ -8739,14 +8739,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="30"/>
-        <v>127935</v>
+        <v>127943</v>
       </c>
       <c r="U45" s="5">
-        <v>264085</v>
+        <v>264093</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="31"/>
-        <v>0.98775798741761978</v>
+        <v>0.98778790984373011</v>
       </c>
       <c r="W45" s="5">
         <v>269851</v>
@@ -8756,14 +8756,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="32"/>
-        <v>57053</v>
+        <v>57064</v>
       </c>
       <c r="Z45" s="5">
-        <v>264057</v>
+        <v>264068</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="33"/>
-        <v>0.97852889186995784</v>
+        <v>0.97856965510596583</v>
       </c>
       <c r="AB45" s="5">
         <v>321990</v>
@@ -8773,14 +8773,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="34"/>
-        <v>161808</v>
+        <v>161821</v>
       </c>
       <c r="AE45" s="5">
-        <v>316931</v>
+        <v>316944</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98428833193577436</v>
+        <v>0.98432870586043042</v>
       </c>
       <c r="AG45" s="5">
         <v>270238</v>
@@ -8790,14 +8790,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="36"/>
-        <v>128180</v>
+        <v>128191</v>
       </c>
       <c r="AJ45" s="5">
-        <v>266771</v>
+        <v>266782</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98717056816583904</v>
+        <v>0.98721127302599931</v>
       </c>
       <c r="AL45" s="5">
         <v>273027</v>
@@ -8807,14 +8807,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="38"/>
-        <v>124452</v>
+        <v>124465</v>
       </c>
       <c r="AO45" s="5">
-        <v>269587</v>
+        <v>269600</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="39"/>
-        <v>0.9874005135023276</v>
+        <v>0.98744812784083624</v>
       </c>
       <c r="AQ45" s="5">
         <v>326184</v>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="40"/>
-        <v>153627</v>
+        <v>153642</v>
       </c>
       <c r="AT45" s="5">
-        <v>323477</v>
+        <v>323492</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="41"/>
-        <v>0.99170100311480636</v>
+        <v>0.99174698942927919</v>
       </c>
       <c r="AV45" s="5">
         <v>274208</v>
@@ -8841,14 +8841,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="42"/>
-        <v>125001</v>
+        <v>125015</v>
       </c>
       <c r="AY45" s="5">
-        <v>272490</v>
+        <v>272504</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="43"/>
-        <v>0.99373468316022873</v>
+        <v>0.99378573929279967</v>
       </c>
       <c r="BA45" s="5">
         <v>277741</v>
@@ -8858,14 +8858,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="44"/>
-        <v>123939</v>
+        <v>123956</v>
       </c>
       <c r="BD45" s="5">
-        <v>274909</v>
+        <v>274926</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98980344997677694</v>
+        <v>0.98986465808072988</v>
       </c>
       <c r="BF45" s="5">
         <v>331328</v>
@@ -8875,14 +8875,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="46"/>
-        <v>167719</v>
+        <v>167745</v>
       </c>
       <c r="BI45" s="5">
-        <v>329691</v>
+        <v>329717</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="47"/>
-        <v>0.99505927660807414</v>
+        <v>0.99513774869615612</v>
       </c>
       <c r="BL45" s="9"/>
     </row>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="E46" s="3">
         <f t="shared" si="24"/>
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F46" s="5">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="25"/>
-        <v>1.0214698596201486</v>
+        <v>1.0218827415359206</v>
       </c>
       <c r="H46" s="5">
         <v>2553</v>
@@ -8918,14 +8918,14 @@
       </c>
       <c r="J46" s="3">
         <f t="shared" si="26"/>
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="K46" s="5">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="27"/>
-        <v>0.99412455934195065</v>
+        <v>0.99451625538582056</v>
       </c>
       <c r="M46" s="5">
         <v>7561</v>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="28"/>
-        <v>4824</v>
+        <v>4825</v>
       </c>
       <c r="P46" s="5">
-        <v>7690</v>
+        <v>7691</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="29"/>
-        <v>1.0170612352863377</v>
+        <v>1.0171934929242163</v>
       </c>
       <c r="R46" s="5">
         <v>2328</v>
@@ -8952,14 +8952,14 @@
       </c>
       <c r="T46" s="3">
         <f t="shared" si="30"/>
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="U46" s="5">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="31"/>
-        <v>1.0231958762886597</v>
+        <v>1.0236254295532645</v>
       </c>
       <c r="W46" s="5">
         <v>2515</v>
@@ -8969,14 +8969,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="32"/>
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Z46" s="5">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="33"/>
-        <v>0.98250497017892646</v>
+        <v>0.9829025844930418</v>
       </c>
       <c r="AB46" s="5">
         <v>7764</v>
@@ -8986,14 +8986,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="34"/>
-        <v>5350</v>
+        <v>5351</v>
       </c>
       <c r="AE46" s="5">
-        <v>7916</v>
+        <v>7917</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0195775373518805</v>
+        <v>1.0197063369397219</v>
       </c>
       <c r="AG46" s="5">
         <v>2401</v>
@@ -9003,14 +9003,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="36"/>
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="37"/>
-        <v>1.0274885464389838</v>
+        <v>1.0279050395668472</v>
       </c>
       <c r="AL46" s="5">
         <v>2561</v>
@@ -9020,14 +9020,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="38"/>
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="AO46" s="5">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="39"/>
-        <v>1.0011714174150723</v>
+        <v>1.0015618898867631</v>
       </c>
       <c r="AQ46" s="5">
         <v>7981</v>
@@ -9037,14 +9037,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="40"/>
-        <v>5065</v>
+        <v>5066</v>
       </c>
       <c r="AT46" s="5">
-        <v>8159</v>
+        <v>8160</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="41"/>
-        <v>1.0223029695526877</v>
+        <v>1.0224282671344442</v>
       </c>
       <c r="AV46" s="5">
         <v>2437</v>
@@ -9054,14 +9054,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="42"/>
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="AY46" s="5">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="43"/>
-        <v>1.0237997537956505</v>
+        <v>1.0242100943783341</v>
       </c>
       <c r="BA46" s="5">
         <v>2592</v>
@@ -9071,14 +9071,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="44"/>
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="BD46" s="5">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="45"/>
-        <v>0.99421296296296291</v>
+        <v>0.99498456790123457</v>
       </c>
       <c r="BF46" s="5">
         <v>8179</v>
@@ -9088,14 +9088,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="46"/>
-        <v>5466</v>
+        <v>5467</v>
       </c>
       <c r="BI46" s="5">
-        <v>8349</v>
+        <v>8350</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="47"/>
-        <v>1.0207849370338673</v>
+        <v>1.0209072013693605</v>
       </c>
       <c r="BL46" s="9"/>
     </row>
@@ -9313,10 +9313,10 @@
       <c r="BL47" s="9"/>
     </row>
     <row r="48" spans="1:64" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="17"/>
+      <c r="B48" s="16"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>8203132</v>
@@ -9327,15 +9327,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3106520</v>
+        <v>3106812</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>8120791</v>
+        <v>8121083</v>
       </c>
       <c r="G48" s="6">
         <f t="shared" si="25"/>
-        <v>0.98996224856554793</v>
+        <v>0.98999784472564867</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9347,15 +9347,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3050716</v>
+        <v>3051039</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>8212702</v>
+        <v>8213025</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" si="27"/>
-        <v>0.98441126462421591</v>
+        <v>0.98444998085164914</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9367,15 +9367,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>5027349</v>
+        <v>5027900</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>12661584</v>
+        <v>12662135</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" si="29"/>
-        <v>0.99324629944371046</v>
+        <v>0.99328952300175766</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9387,15 +9387,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3108530</v>
+        <v>3108906</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>8206364</v>
+        <v>8206740</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" si="31"/>
-        <v>0.99310364524029049</v>
+        <v>0.99314914736164539</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9407,15 +9407,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>1500277</v>
+        <v>1500715</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>8252904</v>
+        <v>8253342</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" si="33"/>
-        <v>0.98069914573729577</v>
+        <v>0.9807511936256309</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9427,15 +9427,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5443812</v>
+        <v>5444576</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>12760113</v>
+        <v>12760877</v>
       </c>
       <c r="AF48" s="6">
         <f t="shared" si="35"/>
-        <v>0.99152047696996515</v>
+        <v>0.99157984334426019</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9447,15 +9447,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>3193992</v>
+        <v>3194513</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8282924</v>
+        <v>8283445</v>
       </c>
       <c r="AK48" s="6">
         <f t="shared" si="37"/>
-        <v>0.99139929580440234</v>
+        <v>0.99146165530849939</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9467,15 +9467,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3012114</v>
+        <v>3012701</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>8366274</v>
+        <v>8366861</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" si="39"/>
-        <v>0.98589715942233924</v>
+        <v>0.98596633258503763</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9487,15 +9487,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4838759</v>
+        <v>4839822</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>12939052</v>
+        <v>12940115</v>
       </c>
       <c r="AU48" s="6">
         <f t="shared" si="41"/>
-        <v>0.99559260258971527</v>
+        <v>0.99567439489849907</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9507,15 +9507,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>3017327</v>
+        <v>3018006</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8438295</v>
+        <v>8438974</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" si="43"/>
-        <v>0.99504523005223977</v>
+        <v>0.99512529785162407</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9527,15 +9527,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3009204</v>
+        <v>3009974</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>8539372</v>
+        <v>8540142</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" si="45"/>
-        <v>0.98782845687302689</v>
+        <v>0.98791752992333937</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9547,20 +9547,25 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5488779</v>
+        <v>5490336</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>13158507</v>
+        <v>13160064</v>
       </c>
       <c r="BJ48" s="6">
         <f t="shared" si="47"/>
-        <v>0.99620075874291847</v>
+        <v>0.99631863568605217</v>
       </c>
       <c r="BL48" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A3:B3"/>
@@ -9574,11 +9579,6 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="AB8:AF8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
